--- a/output_with_grade.xlsx
+++ b/output_with_grade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VX686GH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A9C951-46C2-4079-9F0E-11C3D177332F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07D680C-DB88-4FDD-87BE-69BF923D1FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3941,6 +3941,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-14009]yyyy/mm/dd;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3990,11 +3993,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4304,7 +4311,7 @@
     <col min="1" max="1" width="27.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="154.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.6328125" bestFit="1" customWidth="1"/>
@@ -4337,7 +4344,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -4973,7 +4980,7 @@
       <c r="C10">
         <v>9917151</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>320</v>
       </c>
       <c r="E10">
@@ -5044,7 +5051,7 @@
       <c r="C11">
         <v>9917151</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>320</v>
       </c>
       <c r="E11">
@@ -5115,7 +5122,7 @@
       <c r="C12">
         <v>2172879</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>1301</v>
       </c>
       <c r="E12">
@@ -5186,7 +5193,7 @@
       <c r="C13">
         <v>2195433</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E13">
@@ -5257,7 +5264,7 @@
       <c r="C14">
         <v>8165485</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>1302</v>
       </c>
       <c r="E14">
@@ -5393,7 +5400,7 @@
       <c r="C16">
         <v>2110185</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>1000</v>
       </c>
       <c r="E16">
@@ -5464,7 +5471,7 @@
       <c r="C17">
         <v>2243195</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>481</v>
       </c>
       <c r="E17">
@@ -5535,7 +5542,7 @@
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>582</v>
       </c>
       <c r="E18">
@@ -5677,7 +5684,7 @@
       <c r="C20">
         <v>66632</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>1272</v>
       </c>
       <c r="E20">
@@ -5748,7 +5755,7 @@
       <c r="C21">
         <v>0</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>582</v>
       </c>
       <c r="E21">
@@ -5819,7 +5826,7 @@
       <c r="C22">
         <v>2195433</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E22">
@@ -5890,7 +5897,7 @@
       <c r="C23">
         <v>5103</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>1289</v>
       </c>
       <c r="E23">
@@ -5961,7 +5968,7 @@
       <c r="C24">
         <v>0</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>1281</v>
       </c>
       <c r="E24">
@@ -6032,7 +6039,7 @@
       <c r="C25">
         <v>249</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>463</v>
       </c>
       <c r="E25">
@@ -6103,7 +6110,7 @@
       <c r="C26">
         <v>0</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="E26">
@@ -6174,7 +6181,7 @@
       <c r="C27">
         <v>7462449</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>1286</v>
       </c>
       <c r="E27">
@@ -6245,7 +6252,7 @@
       <c r="C28">
         <v>0</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>1289</v>
       </c>
       <c r="E28">
@@ -6316,7 +6323,7 @@
       <c r="C29">
         <v>0</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>395</v>
       </c>
       <c r="E29">
@@ -6387,7 +6394,7 @@
       <c r="C30">
         <v>0</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
         <v>405</v>
       </c>
       <c r="E30">
@@ -6458,7 +6465,7 @@
       <c r="C31">
         <v>0</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="3" t="s">
         <v>1281</v>
       </c>
       <c r="E31">
@@ -6529,7 +6536,7 @@
       <c r="C32">
         <v>0</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="3" t="s">
         <v>1276</v>
       </c>
       <c r="E32">
@@ -6600,7 +6607,7 @@
       <c r="C33">
         <v>2021535</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="E33">
@@ -6671,7 +6678,7 @@
       <c r="C34">
         <v>0</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="3" t="s">
         <v>1274</v>
       </c>
       <c r="E34">
@@ -6742,7 +6749,7 @@
       <c r="C35">
         <v>4</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="3" t="s">
         <v>395</v>
       </c>
       <c r="E35">
@@ -6813,7 +6820,7 @@
       <c r="C36">
         <v>0</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="3" t="s">
         <v>437</v>
       </c>
       <c r="E36">
@@ -6884,7 +6891,7 @@
       <c r="C37">
         <v>5766561</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="3" t="s">
         <v>1272</v>
       </c>
       <c r="E37">
@@ -6955,7 +6962,7 @@
       <c r="C38">
         <v>0</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="3" t="s">
         <v>395</v>
       </c>
       <c r="E38">
@@ -7026,7 +7033,7 @@
       <c r="C39">
         <v>15</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="3" t="s">
         <v>1252</v>
       </c>
       <c r="E39">
@@ -7097,7 +7104,7 @@
       <c r="C40">
         <v>15</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="3" t="s">
         <v>1252</v>
       </c>
       <c r="E40">
@@ -7168,7 +7175,7 @@
       <c r="C41">
         <v>0</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="3" t="s">
         <v>1269</v>
       </c>
       <c r="E41">
@@ -7239,7 +7246,7 @@
       <c r="C42">
         <v>8579</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="3" t="s">
         <v>437</v>
       </c>
       <c r="E42">
@@ -7310,7 +7317,7 @@
       <c r="C43">
         <v>15</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="3" t="s">
         <v>1252</v>
       </c>
       <c r="E43">
@@ -7381,7 +7388,7 @@
       <c r="C44">
         <v>69744</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="3" t="s">
         <v>926</v>
       </c>
       <c r="E44">
@@ -7452,7 +7459,7 @@
       <c r="C45">
         <v>0</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="3" t="s">
         <v>582</v>
       </c>
       <c r="E45">
@@ -7523,7 +7530,7 @@
       <c r="C46">
         <v>0</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="3" t="s">
         <v>1267</v>
       </c>
       <c r="E46">
@@ -7594,7 +7601,7 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="3" t="s">
         <v>432</v>
       </c>
       <c r="E47">
@@ -7665,7 +7672,7 @@
       <c r="C48">
         <v>4</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="3" t="s">
         <v>432</v>
       </c>
       <c r="E48">
@@ -7736,7 +7743,7 @@
       <c r="C49">
         <v>0</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="3" t="s">
         <v>437</v>
       </c>
       <c r="E49">
@@ -7807,7 +7814,7 @@
       <c r="C50">
         <v>27</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="3" t="s">
         <v>405</v>
       </c>
       <c r="E50">
@@ -7878,7 +7885,7 @@
       <c r="C51">
         <v>0</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="3" t="s">
         <v>1259</v>
       </c>
       <c r="E51">
@@ -8020,7 +8027,7 @@
       <c r="C53">
         <v>2185872</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E53">
@@ -8091,7 +8098,7 @@
       <c r="C54">
         <v>15</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="3" t="s">
         <v>1252</v>
       </c>
       <c r="E54">
@@ -8233,7 +8240,7 @@
       <c r="C56">
         <v>0</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="3" t="s">
         <v>582</v>
       </c>
       <c r="E56">
@@ -8304,7 +8311,7 @@
       <c r="C57">
         <v>2195433</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E57">
@@ -8375,7 +8382,7 @@
       <c r="C58">
         <v>710</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="3" t="s">
         <v>1255</v>
       </c>
       <c r="E58">
@@ -8446,7 +8453,7 @@
       <c r="C59">
         <v>15</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="3" t="s">
         <v>1252</v>
       </c>
       <c r="E59">
@@ -8517,7 +8524,7 @@
       <c r="C60">
         <v>0</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="3" t="s">
         <v>582</v>
       </c>
       <c r="E60">
@@ -8659,7 +8666,7 @@
       <c r="C62">
         <v>0</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="3" t="s">
         <v>494</v>
       </c>
       <c r="E62">
@@ -8730,7 +8737,7 @@
       <c r="C63">
         <v>0</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="3" t="s">
         <v>494</v>
       </c>
       <c r="E63">
@@ -8801,7 +8808,7 @@
       <c r="C64">
         <v>0</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="3" t="s">
         <v>494</v>
       </c>
       <c r="E64">
@@ -8943,7 +8950,7 @@
       <c r="C66">
         <v>0</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="3" t="s">
         <v>494</v>
       </c>
       <c r="E66">
@@ -9085,7 +9092,7 @@
       <c r="C68">
         <v>0</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="3" t="s">
         <v>494</v>
       </c>
       <c r="E68">
@@ -9298,7 +9305,7 @@
       <c r="C71">
         <v>2195433</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E71">
@@ -9369,7 +9376,7 @@
       <c r="C72">
         <v>2251440</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="3" t="s">
         <v>309</v>
       </c>
       <c r="E72">
@@ -9440,7 +9447,7 @@
       <c r="C73">
         <v>0</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="3" t="s">
         <v>1244</v>
       </c>
       <c r="E73">
@@ -9511,7 +9518,7 @@
       <c r="C74">
         <v>0</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="3" t="s">
         <v>1244</v>
       </c>
       <c r="E74">
@@ -9582,7 +9589,7 @@
       <c r="C75">
         <v>0</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="3" t="s">
         <v>1244</v>
       </c>
       <c r="E75">
@@ -9653,7 +9660,7 @@
       <c r="C76">
         <v>0</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="3" t="s">
         <v>1244</v>
       </c>
       <c r="E76">
@@ -9724,7 +9731,7 @@
       <c r="C77">
         <v>0</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="3" t="s">
         <v>1244</v>
       </c>
       <c r="E77">
@@ -9795,7 +9802,7 @@
       <c r="C78">
         <v>0</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="3" t="s">
         <v>1238</v>
       </c>
       <c r="E78">
@@ -9866,7 +9873,7 @@
       <c r="C79">
         <v>2303887</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="3" t="s">
         <v>319</v>
       </c>
       <c r="E79">
@@ -9937,7 +9944,7 @@
       <c r="C80">
         <v>0</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="3" t="s">
         <v>1107</v>
       </c>
       <c r="E80">
@@ -9993,7 +10000,7 @@
       <c r="C81">
         <v>0</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="3" t="s">
         <v>1222</v>
       </c>
       <c r="E81">
@@ -10049,7 +10056,7 @@
       <c r="C82">
         <v>0</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="3" t="s">
         <v>1244</v>
       </c>
       <c r="E82">
@@ -10120,7 +10127,7 @@
       <c r="C83">
         <v>0</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="3" t="s">
         <v>1211</v>
       </c>
       <c r="E83">
@@ -10191,7 +10198,7 @@
       <c r="C84">
         <v>0</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="3" t="s">
         <v>1139</v>
       </c>
       <c r="E84">
@@ -10262,7 +10269,7 @@
       <c r="C85">
         <v>0</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="3" t="s">
         <v>1139</v>
       </c>
       <c r="E85">
@@ -10333,7 +10340,7 @@
       <c r="C86">
         <v>0</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="3" t="s">
         <v>1108</v>
       </c>
       <c r="E86">
@@ -10389,7 +10396,7 @@
       <c r="C87">
         <v>2232920</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="3" t="s">
         <v>481</v>
       </c>
       <c r="E87">
@@ -10460,7 +10467,7 @@
       <c r="C88">
         <v>2057953</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="3" t="s">
         <v>1216</v>
       </c>
       <c r="E88">
@@ -10531,7 +10538,7 @@
       <c r="C89">
         <v>2199059</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E89">
@@ -10602,7 +10609,7 @@
       <c r="C90">
         <v>2354291</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E90">
@@ -10673,7 +10680,7 @@
       <c r="C91">
         <v>0</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="3" t="s">
         <v>1220</v>
       </c>
       <c r="E91">
@@ -10729,7 +10736,7 @@
       <c r="C92">
         <v>0</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="3" t="s">
         <v>1222</v>
       </c>
       <c r="E92">
@@ -10785,7 +10792,7 @@
       <c r="C93">
         <v>0</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="3" t="s">
         <v>1220</v>
       </c>
       <c r="E93">
@@ -10841,7 +10848,7 @@
       <c r="C94">
         <v>0</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="3" t="s">
         <v>1218</v>
       </c>
       <c r="E94">
@@ -10897,7 +10904,7 @@
       <c r="C95">
         <v>0</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="3" t="s">
         <v>1220</v>
       </c>
       <c r="E95">
@@ -10953,7 +10960,7 @@
       <c r="C96">
         <v>0</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="3" t="s">
         <v>1220</v>
       </c>
       <c r="E96">
@@ -11009,7 +11016,7 @@
       <c r="C97">
         <v>0</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="3" t="s">
         <v>1220</v>
       </c>
       <c r="E97">
@@ -11065,7 +11072,7 @@
       <c r="C98">
         <v>0</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="3" t="s">
         <v>1225</v>
       </c>
       <c r="E98">
@@ -11121,7 +11128,7 @@
       <c r="C99">
         <v>0</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="3" t="s">
         <v>1218</v>
       </c>
       <c r="E99">
@@ -11319,7 +11326,7 @@
       <c r="C102">
         <v>0</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="3" t="s">
         <v>1225</v>
       </c>
       <c r="E102">
@@ -11375,7 +11382,7 @@
       <c r="C103">
         <v>0</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="3" t="s">
         <v>1238</v>
       </c>
       <c r="E103">
@@ -11446,7 +11453,7 @@
       <c r="C104">
         <v>0</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="3" t="s">
         <v>1138</v>
       </c>
       <c r="E104">
@@ -11517,7 +11524,7 @@
       <c r="C105">
         <v>0</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="3" t="s">
         <v>1243</v>
       </c>
       <c r="E105">
@@ -11659,7 +11666,7 @@
       <c r="C107">
         <v>0</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="3" t="s">
         <v>366</v>
       </c>
       <c r="E107">
@@ -11730,7 +11737,7 @@
       <c r="C108">
         <v>0</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="3" t="s">
         <v>366</v>
       </c>
       <c r="E108">
@@ -11801,7 +11808,7 @@
       <c r="C109">
         <v>0</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="3" t="s">
         <v>1197</v>
       </c>
       <c r="E109">
@@ -11943,7 +11950,7 @@
       <c r="C111">
         <v>0</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="3" t="s">
         <v>1191</v>
       </c>
       <c r="E111">
@@ -12014,7 +12021,7 @@
       <c r="C112">
         <v>0</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="3" t="s">
         <v>1238</v>
       </c>
       <c r="E112">
@@ -12085,7 +12092,7 @@
       <c r="C113">
         <v>0</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="3" t="s">
         <v>1238</v>
       </c>
       <c r="E113">
@@ -12156,7 +12163,7 @@
       <c r="C114">
         <v>0</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="3" t="s">
         <v>1238</v>
       </c>
       <c r="E114">
@@ -12227,7 +12234,7 @@
       <c r="C115">
         <v>2008379</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="3" t="s">
         <v>373</v>
       </c>
       <c r="E115">
@@ -12369,7 +12376,7 @@
       <c r="C117">
         <v>2118969</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="3" t="s">
         <v>1000</v>
       </c>
       <c r="E117">
@@ -12440,7 +12447,7 @@
       <c r="C118">
         <v>9949745</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="3" t="s">
         <v>1209</v>
       </c>
       <c r="E118">
@@ -12508,7 +12515,7 @@
       <c r="C119">
         <v>9894635</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="3" t="s">
         <v>101</v>
       </c>
       <c r="E119">
@@ -12579,7 +12586,7 @@
       <c r="C120">
         <v>9924868</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="3" t="s">
         <v>320</v>
       </c>
       <c r="E120">
@@ -12650,7 +12657,7 @@
       <c r="C121">
         <v>2321168</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E121">
@@ -12718,7 +12725,7 @@
       <c r="C122">
         <v>2149974</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="3" t="s">
         <v>1204</v>
       </c>
       <c r="E122">
@@ -12789,7 +12796,7 @@
       <c r="C123">
         <v>2017336</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="E123">
@@ -12860,7 +12867,7 @@
       <c r="C124">
         <v>0</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="3" t="s">
         <v>1200</v>
       </c>
       <c r="E124">
@@ -12931,7 +12938,7 @@
       <c r="C125">
         <v>0</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="3" t="s">
         <v>1191</v>
       </c>
       <c r="E125">
@@ -13002,7 +13009,7 @@
       <c r="C126">
         <v>0</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="3" t="s">
         <v>1191</v>
       </c>
       <c r="E126">
@@ -13073,7 +13080,7 @@
       <c r="C127">
         <v>0</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="3" t="s">
         <v>1191</v>
       </c>
       <c r="E127">
@@ -13144,7 +13151,7 @@
       <c r="C128">
         <v>0</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="3" t="s">
         <v>1191</v>
       </c>
       <c r="E128">
@@ -13215,7 +13222,7 @@
       <c r="C129">
         <v>0</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="3" t="s">
         <v>1197</v>
       </c>
       <c r="E129">
@@ -13286,7 +13293,7 @@
       <c r="C130">
         <v>0</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="3" t="s">
         <v>1191</v>
       </c>
       <c r="E130">
@@ -13357,7 +13364,7 @@
       <c r="C131">
         <v>2303884</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="3" t="s">
         <v>319</v>
       </c>
       <c r="E131">
@@ -13428,7 +13435,7 @@
       <c r="C132">
         <v>9924478</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="3" t="s">
         <v>320</v>
       </c>
       <c r="E132">
@@ -13499,7 +13506,7 @@
       <c r="C133">
         <v>7901665</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="3" t="s">
         <v>1013</v>
       </c>
       <c r="E133">
@@ -13570,7 +13577,7 @@
       <c r="C134">
         <v>7901665</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="3" t="s">
         <v>1013</v>
       </c>
       <c r="E134">
@@ -13641,7 +13648,7 @@
       <c r="C135">
         <v>7580514</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E135">
@@ -13712,7 +13719,7 @@
       <c r="C136">
         <v>7667090</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="3" t="s">
         <v>793</v>
       </c>
       <c r="E136">
@@ -13854,7 +13861,7 @@
       <c r="C138">
         <v>9868709</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D138" s="3" t="s">
         <v>1180</v>
       </c>
       <c r="E138">
@@ -13925,7 +13932,7 @@
       <c r="C139">
         <v>2319638</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E139">
@@ -14067,7 +14074,7 @@
       <c r="C141">
         <v>9114887</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D141" s="3" t="s">
         <v>1145</v>
       </c>
       <c r="E141">
@@ -14138,7 +14145,7 @@
       <c r="C142">
         <v>9114887</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="3" t="s">
         <v>1145</v>
       </c>
       <c r="E142">
@@ -14209,7 +14216,7 @@
       <c r="C143">
         <v>9208699</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D143" s="3" t="s">
         <v>1175</v>
       </c>
       <c r="E143">
@@ -14280,7 +14287,7 @@
       <c r="C144">
         <v>9208699</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="3" t="s">
         <v>1175</v>
       </c>
       <c r="E144">
@@ -14351,7 +14358,7 @@
       <c r="C145">
         <v>9208699</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D145" s="3" t="s">
         <v>1175</v>
       </c>
       <c r="E145">
@@ -14422,7 +14429,7 @@
       <c r="C146">
         <v>9208699</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="3" t="s">
         <v>1175</v>
       </c>
       <c r="E146">
@@ -14493,7 +14500,7 @@
       <c r="C147">
         <v>9208699</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D147" s="3" t="s">
         <v>1175</v>
       </c>
       <c r="E147">
@@ -14564,7 +14571,7 @@
       <c r="C148">
         <v>8796166</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E148">
@@ -14635,7 +14642,7 @@
       <c r="C149">
         <v>9018463</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D149" s="3" t="s">
         <v>1171</v>
       </c>
       <c r="E149">
@@ -14706,7 +14713,7 @@
       <c r="C150">
         <v>8795965</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D150" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E150">
@@ -14777,7 +14784,7 @@
       <c r="C151">
         <v>8661395</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D151" s="3" t="s">
         <v>1114</v>
       </c>
       <c r="E151">
@@ -14848,7 +14855,7 @@
       <c r="C152">
         <v>8764290</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D152" s="3" t="s">
         <v>1125</v>
       </c>
       <c r="E152">
@@ -14919,7 +14926,7 @@
       <c r="C153">
         <v>8894671</v>
       </c>
-      <c r="D153" t="s">
+      <c r="D153" s="3" t="s">
         <v>717</v>
       </c>
       <c r="E153">
@@ -14990,7 +14997,7 @@
       <c r="C154">
         <v>9025351</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D154" s="3" t="s">
         <v>1171</v>
       </c>
       <c r="E154">
@@ -15061,7 +15068,7 @@
       <c r="C155">
         <v>8929268</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D155" s="3" t="s">
         <v>691</v>
       </c>
       <c r="E155">
@@ -15132,7 +15139,7 @@
       <c r="C156">
         <v>8800014</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D156" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E156">
@@ -15203,7 +15210,7 @@
       <c r="C157">
         <v>8805708</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D157" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E157">
@@ -15274,7 +15281,7 @@
       <c r="C158">
         <v>8691711</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D158" s="3" t="s">
         <v>1164</v>
       </c>
       <c r="E158">
@@ -15345,7 +15352,7 @@
       <c r="C159">
         <v>8805708</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D159" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E159">
@@ -15416,7 +15423,7 @@
       <c r="C160">
         <v>8710888</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D160" s="3" t="s">
         <v>1131</v>
       </c>
       <c r="E160">
@@ -15487,7 +15494,7 @@
       <c r="C161">
         <v>8760193</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D161" s="3" t="s">
         <v>1125</v>
       </c>
       <c r="E161">
@@ -15558,7 +15565,7 @@
       <c r="C162">
         <v>0</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D162" s="3" t="s">
         <v>1140</v>
       </c>
       <c r="E162">
@@ -15629,7 +15636,7 @@
       <c r="C163">
         <v>8921220</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D163" s="3" t="s">
         <v>691</v>
       </c>
       <c r="E163">
@@ -15700,7 +15707,7 @@
       <c r="C164">
         <v>8890186</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D164" s="3" t="s">
         <v>1157</v>
       </c>
       <c r="E164">
@@ -15771,7 +15778,7 @@
       <c r="C165">
         <v>8836883</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D165" s="3" t="s">
         <v>1158</v>
       </c>
       <c r="E165">
@@ -15842,7 +15849,7 @@
       <c r="C166">
         <v>8748641</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="3" t="s">
         <v>1125</v>
       </c>
       <c r="E166">
@@ -15913,7 +15920,7 @@
       <c r="C167">
         <v>8820088</v>
       </c>
-      <c r="D167" t="s">
+      <c r="D167" s="3" t="s">
         <v>1152</v>
       </c>
       <c r="E167">
@@ -15984,7 +15991,7 @@
       <c r="C168">
         <v>2021535</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D168" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="E168">
@@ -16055,7 +16062,7 @@
       <c r="C169">
         <v>2305615</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D169" s="3" t="s">
         <v>319</v>
       </c>
       <c r="E169">
@@ -16126,7 +16133,7 @@
       <c r="C170">
         <v>2305615</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D170" s="3" t="s">
         <v>319</v>
       </c>
       <c r="E170">
@@ -16197,7 +16204,7 @@
       <c r="C171">
         <v>3865819</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D171" s="3" t="s">
         <v>889</v>
       </c>
       <c r="E171">
@@ -16262,7 +16269,7 @@
       <c r="C172">
         <v>9103384</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D172" s="3" t="s">
         <v>1145</v>
       </c>
       <c r="E172">
@@ -16333,7 +16340,7 @@
       <c r="C173">
         <v>3888115</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D173" s="3" t="s">
         <v>904</v>
       </c>
       <c r="E173">
@@ -16398,7 +16405,7 @@
       <c r="C174">
         <v>0</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D174" s="3" t="s">
         <v>1139</v>
       </c>
       <c r="E174">
@@ -16469,7 +16476,7 @@
       <c r="C175">
         <v>0</v>
       </c>
-      <c r="D175" t="s">
+      <c r="D175" s="3" t="s">
         <v>1138</v>
       </c>
       <c r="E175">
@@ -16682,7 +16689,7 @@
       <c r="C178">
         <v>0</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D178" s="3" t="s">
         <v>1140</v>
       </c>
       <c r="E178">
@@ -16753,7 +16760,7 @@
       <c r="C179">
         <v>0</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="3" t="s">
         <v>1139</v>
       </c>
       <c r="E179">
@@ -16824,7 +16831,7 @@
       <c r="C180">
         <v>0</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="3" t="s">
         <v>1138</v>
       </c>
       <c r="E180">
@@ -16895,7 +16902,7 @@
       <c r="C181">
         <v>0</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D181" s="3" t="s">
         <v>975</v>
       </c>
       <c r="E181">
@@ -16966,7 +16973,7 @@
       <c r="C182">
         <v>2110185</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="3" t="s">
         <v>1000</v>
       </c>
       <c r="E182">
@@ -17037,7 +17044,7 @@
       <c r="C183">
         <v>3464864</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="3" t="s">
         <v>1032</v>
       </c>
       <c r="E183">
@@ -17108,7 +17115,7 @@
       <c r="C184">
         <v>0</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="3" t="s">
         <v>1105</v>
       </c>
       <c r="E184">
@@ -17164,7 +17171,7 @@
       <c r="C185">
         <v>3587031</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D185" s="3" t="s">
         <v>1039</v>
       </c>
       <c r="E185">
@@ -17235,7 +17242,7 @@
       <c r="C186">
         <v>3542044</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D186" s="3" t="s">
         <v>1041</v>
       </c>
       <c r="E186">
@@ -17303,7 +17310,7 @@
       <c r="C187">
         <v>3453229</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D187" s="3" t="s">
         <v>1032</v>
       </c>
       <c r="E187">
@@ -17374,7 +17381,7 @@
       <c r="C188">
         <v>3207017</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D188" s="3" t="s">
         <v>1046</v>
       </c>
       <c r="E188">
@@ -17445,7 +17452,7 @@
       <c r="C189">
         <v>3607580</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D189" s="3" t="s">
         <v>1037</v>
       </c>
       <c r="E189">
@@ -17516,7 +17523,7 @@
       <c r="C190">
         <v>0</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D190" s="3" t="s">
         <v>1108</v>
       </c>
       <c r="E190">
@@ -17572,7 +17579,7 @@
       <c r="C191">
         <v>0</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D191" s="3" t="s">
         <v>1104</v>
       </c>
       <c r="E191">
@@ -17628,7 +17635,7 @@
       <c r="C192">
         <v>8641052</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D192" s="3" t="s">
         <v>1126</v>
       </c>
       <c r="E192">
@@ -17699,7 +17706,7 @@
       <c r="C193">
         <v>8640987</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D193" s="3" t="s">
         <v>1126</v>
       </c>
       <c r="E193">
@@ -17770,7 +17777,7 @@
       <c r="C194">
         <v>8980901</v>
       </c>
-      <c r="D194" t="s">
+      <c r="D194" s="3" t="s">
         <v>701</v>
       </c>
       <c r="E194">
@@ -17841,7 +17848,7 @@
       <c r="C195">
         <v>8870552</v>
       </c>
-      <c r="D195" t="s">
+      <c r="D195" s="3" t="s">
         <v>1135</v>
       </c>
       <c r="E195">
@@ -17912,7 +17919,7 @@
       <c r="C196">
         <v>8870564</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D196" s="3" t="s">
         <v>1135</v>
       </c>
       <c r="E196">
@@ -17983,7 +17990,7 @@
       <c r="C197">
         <v>8452130</v>
       </c>
-      <c r="D197" t="s">
+      <c r="D197" s="3" t="s">
         <v>1029</v>
       </c>
       <c r="E197">
@@ -18054,7 +18061,7 @@
       <c r="C198">
         <v>0</v>
       </c>
-      <c r="D198" t="s">
+      <c r="D198" s="3" t="s">
         <v>1107</v>
       </c>
       <c r="E198">
@@ -18110,7 +18117,7 @@
       <c r="C199">
         <v>0</v>
       </c>
-      <c r="D199" t="s">
+      <c r="D199" s="3" t="s">
         <v>1107</v>
       </c>
       <c r="E199">
@@ -18166,7 +18173,7 @@
       <c r="C200">
         <v>0</v>
       </c>
-      <c r="D200" t="s">
+      <c r="D200" s="3" t="s">
         <v>1107</v>
       </c>
       <c r="E200">
@@ -18222,7 +18229,7 @@
       <c r="C201">
         <v>8369443</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D201" s="3" t="s">
         <v>1056</v>
       </c>
       <c r="E201">
@@ -18293,7 +18300,7 @@
       <c r="C202">
         <v>0</v>
       </c>
-      <c r="D202" t="s">
+      <c r="D202" s="3" t="s">
         <v>975</v>
       </c>
       <c r="E202">
@@ -18364,7 +18371,7 @@
       <c r="C203">
         <v>0</v>
       </c>
-      <c r="D203" t="s">
+      <c r="D203" s="3" t="s">
         <v>1090</v>
       </c>
       <c r="E203">
@@ -18435,7 +18442,7 @@
       <c r="C204">
         <v>0</v>
       </c>
-      <c r="D204" t="s">
+      <c r="D204" s="3" t="s">
         <v>973</v>
       </c>
       <c r="E204">
@@ -18506,7 +18513,7 @@
       <c r="C205">
         <v>0</v>
       </c>
-      <c r="D205" t="s">
+      <c r="D205" s="3" t="s">
         <v>1067</v>
       </c>
       <c r="E205">
@@ -18577,7 +18584,7 @@
       <c r="C206">
         <v>0</v>
       </c>
-      <c r="D206" t="s">
+      <c r="D206" s="3" t="s">
         <v>646</v>
       </c>
       <c r="E206">
@@ -18648,7 +18655,7 @@
       <c r="C207">
         <v>0</v>
       </c>
-      <c r="D207" t="s">
+      <c r="D207" s="3" t="s">
         <v>654</v>
       </c>
       <c r="E207">
@@ -18719,7 +18726,7 @@
       <c r="C208">
         <v>0</v>
       </c>
-      <c r="D208" t="s">
+      <c r="D208" s="3" t="s">
         <v>646</v>
       </c>
       <c r="E208">
@@ -18790,7 +18797,7 @@
       <c r="C209">
         <v>0</v>
       </c>
-      <c r="D209" t="s">
+      <c r="D209" s="3" t="s">
         <v>984</v>
       </c>
       <c r="E209">
@@ -18861,7 +18868,7 @@
       <c r="C210">
         <v>0</v>
       </c>
-      <c r="D210" t="s">
+      <c r="D210" s="3" t="s">
         <v>996</v>
       </c>
       <c r="E210">
@@ -18932,7 +18939,7 @@
       <c r="C211">
         <v>0</v>
       </c>
-      <c r="D211" t="s">
+      <c r="D211" s="3" t="s">
         <v>996</v>
       </c>
       <c r="E211">
@@ -19003,7 +19010,7 @@
       <c r="C212">
         <v>7813279</v>
       </c>
-      <c r="D212" t="s">
+      <c r="D212" s="3" t="s">
         <v>994</v>
       </c>
       <c r="E212">
@@ -19074,7 +19081,7 @@
       <c r="C213">
         <v>7605715</v>
       </c>
-      <c r="D213" t="s">
+      <c r="D213" s="3" t="s">
         <v>84</v>
       </c>
       <c r="E213">
@@ -19145,7 +19152,7 @@
       <c r="C214">
         <v>8466238</v>
       </c>
-      <c r="D214" t="s">
+      <c r="D214" s="3" t="s">
         <v>1054</v>
       </c>
       <c r="E214">
@@ -19216,7 +19223,7 @@
       <c r="C215">
         <v>8392817</v>
       </c>
-      <c r="D215" t="s">
+      <c r="D215" s="3" t="s">
         <v>1055</v>
       </c>
       <c r="E215">
@@ -19287,7 +19294,7 @@
       <c r="C216">
         <v>9036264</v>
       </c>
-      <c r="D216" t="s">
+      <c r="D216" s="3" t="s">
         <v>1110</v>
       </c>
       <c r="E216">
@@ -19358,7 +19365,7 @@
       <c r="C217">
         <v>3556499</v>
       </c>
-      <c r="D217" t="s">
+      <c r="D217" s="3" t="s">
         <v>1034</v>
       </c>
       <c r="E217">
@@ -19429,7 +19436,7 @@
       <c r="C218">
         <v>3532476</v>
       </c>
-      <c r="D218" t="s">
+      <c r="D218" s="3" t="s">
         <v>1041</v>
       </c>
       <c r="E218">
@@ -19500,7 +19507,7 @@
       <c r="C219">
         <v>3575753</v>
       </c>
-      <c r="D219" t="s">
+      <c r="D219" s="3" t="s">
         <v>1039</v>
       </c>
       <c r="E219">
@@ -19571,7 +19578,7 @@
       <c r="C220">
         <v>8759244</v>
       </c>
-      <c r="D220" t="s">
+      <c r="D220" s="3" t="s">
         <v>1125</v>
       </c>
       <c r="E220">
@@ -19642,7 +19649,7 @@
       <c r="C221">
         <v>7792304</v>
       </c>
-      <c r="D221" t="s">
+      <c r="D221" s="3" t="s">
         <v>986</v>
       </c>
       <c r="E221">
@@ -19713,7 +19720,7 @@
       <c r="C222">
         <v>8316238</v>
       </c>
-      <c r="D222" t="s">
+      <c r="D222" s="3" t="s">
         <v>1027</v>
       </c>
       <c r="E222">
@@ -19784,7 +19791,7 @@
       <c r="C223">
         <v>8445415</v>
       </c>
-      <c r="D223" t="s">
+      <c r="D223" s="3" t="s">
         <v>1029</v>
       </c>
       <c r="E223">
@@ -19855,7 +19862,7 @@
       <c r="C224">
         <v>7922508</v>
       </c>
-      <c r="D224" t="s">
+      <c r="D224" s="3" t="s">
         <v>929</v>
       </c>
       <c r="E224">
@@ -19926,7 +19933,7 @@
       <c r="C225">
         <v>2195433</v>
       </c>
-      <c r="D225" t="s">
+      <c r="D225" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E225">
@@ -19997,7 +20004,7 @@
       <c r="C226">
         <v>2195433</v>
       </c>
-      <c r="D226" t="s">
+      <c r="D226" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E226">
@@ -20068,7 +20075,7 @@
       <c r="C227">
         <v>2195433</v>
       </c>
-      <c r="D227" t="s">
+      <c r="D227" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E227">
@@ -20139,7 +20146,7 @@
       <c r="C228">
         <v>2195433</v>
       </c>
-      <c r="D228" t="s">
+      <c r="D228" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E228">
@@ -20210,7 +20217,7 @@
       <c r="C229">
         <v>2195433</v>
       </c>
-      <c r="D229" t="s">
+      <c r="D229" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E229">
@@ -20281,7 +20288,7 @@
       <c r="C230">
         <v>7651108</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D230" s="3" t="s">
         <v>248</v>
       </c>
       <c r="E230">
@@ -20352,7 +20359,7 @@
       <c r="C231">
         <v>8803232</v>
       </c>
-      <c r="D231" t="s">
+      <c r="D231" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E231">
@@ -20423,7 +20430,7 @@
       <c r="C232">
         <v>8710647</v>
       </c>
-      <c r="D232" t="s">
+      <c r="D232" s="3" t="s">
         <v>1131</v>
       </c>
       <c r="E232">
@@ -20494,7 +20501,7 @@
       <c r="C233">
         <v>8710647</v>
       </c>
-      <c r="D233" t="s">
+      <c r="D233" s="3" t="s">
         <v>1131</v>
       </c>
       <c r="E233">
@@ -20565,7 +20572,7 @@
       <c r="C234">
         <v>8710647</v>
       </c>
-      <c r="D234" t="s">
+      <c r="D234" s="3" t="s">
         <v>1131</v>
       </c>
       <c r="E234">
@@ -20636,7 +20643,7 @@
       <c r="C235">
         <v>0</v>
       </c>
-      <c r="D235" t="s">
+      <c r="D235" s="3" t="s">
         <v>1104</v>
       </c>
       <c r="E235">
@@ -20692,7 +20699,7 @@
       <c r="C236">
         <v>3898726</v>
       </c>
-      <c r="D236" t="s">
+      <c r="D236" s="3" t="s">
         <v>904</v>
       </c>
       <c r="E236">
@@ -20757,7 +20764,7 @@
       <c r="C237">
         <v>8634077</v>
       </c>
-      <c r="D237" t="s">
+      <c r="D237" s="3" t="s">
         <v>1126</v>
       </c>
       <c r="E237">
@@ -20828,7 +20835,7 @@
       <c r="C238">
         <v>3837649</v>
       </c>
-      <c r="D238" t="s">
+      <c r="D238" s="3" t="s">
         <v>385</v>
       </c>
       <c r="E238">
@@ -20893,7 +20900,7 @@
       <c r="C239">
         <v>3837649</v>
       </c>
-      <c r="D239" t="s">
+      <c r="D239" s="3" t="s">
         <v>385</v>
       </c>
       <c r="E239">
@@ -20958,7 +20965,7 @@
       <c r="C240">
         <v>8265036</v>
       </c>
-      <c r="D240" t="s">
+      <c r="D240" s="3" t="s">
         <v>1062</v>
       </c>
       <c r="E240">
@@ -21029,7 +21036,7 @@
       <c r="C241">
         <v>3825704</v>
       </c>
-      <c r="D241" t="s">
+      <c r="D241" s="3" t="s">
         <v>410</v>
       </c>
       <c r="E241">
@@ -21165,7 +21172,7 @@
       <c r="C243">
         <v>3825704</v>
       </c>
-      <c r="D243" t="s">
+      <c r="D243" s="3" t="s">
         <v>410</v>
       </c>
       <c r="E243">
@@ -21230,7 +21237,7 @@
       <c r="C244">
         <v>0</v>
       </c>
-      <c r="D244" t="s">
+      <c r="D244" s="3" t="s">
         <v>979</v>
       </c>
       <c r="E244">
@@ -21301,7 +21308,7 @@
       <c r="C245">
         <v>0</v>
       </c>
-      <c r="D245" t="s">
+      <c r="D245" s="3" t="s">
         <v>1009</v>
       </c>
       <c r="E245">
@@ -21372,7 +21379,7 @@
       <c r="C246">
         <v>0</v>
       </c>
-      <c r="D246" t="s">
+      <c r="D246" s="3" t="s">
         <v>1010</v>
       </c>
       <c r="E246">
@@ -21443,7 +21450,7 @@
       <c r="C247">
         <v>0</v>
       </c>
-      <c r="D247" t="s">
+      <c r="D247" s="3" t="s">
         <v>985</v>
       </c>
       <c r="E247">
@@ -21514,7 +21521,7 @@
       <c r="C248">
         <v>0</v>
       </c>
-      <c r="D248" t="s">
+      <c r="D248" s="3" t="s">
         <v>956</v>
       </c>
       <c r="E248">
@@ -21585,7 +21592,7 @@
       <c r="C249">
         <v>0</v>
       </c>
-      <c r="D249" t="s">
+      <c r="D249" s="3" t="s">
         <v>956</v>
       </c>
       <c r="E249">
@@ -21656,7 +21663,7 @@
       <c r="C250">
         <v>0</v>
       </c>
-      <c r="D250" t="s">
+      <c r="D250" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E250">
@@ -21798,7 +21805,7 @@
       <c r="C252">
         <v>0</v>
       </c>
-      <c r="D252" t="s">
+      <c r="D252" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E252">
@@ -21869,7 +21876,7 @@
       <c r="C253">
         <v>0</v>
       </c>
-      <c r="D253" t="s">
+      <c r="D253" s="3" t="s">
         <v>654</v>
       </c>
       <c r="E253">
@@ -21940,7 +21947,7 @@
       <c r="C254">
         <v>0</v>
       </c>
-      <c r="D254" t="s">
+      <c r="D254" s="3" t="s">
         <v>646</v>
       </c>
       <c r="E254">
@@ -22011,7 +22018,7 @@
       <c r="C255">
         <v>0</v>
       </c>
-      <c r="D255" t="s">
+      <c r="D255" s="3" t="s">
         <v>1006</v>
       </c>
       <c r="E255">
@@ -22082,7 +22089,7 @@
       <c r="C256">
         <v>0</v>
       </c>
-      <c r="D256" t="s">
+      <c r="D256" s="3" t="s">
         <v>1006</v>
       </c>
       <c r="E256">
@@ -22153,7 +22160,7 @@
       <c r="C257">
         <v>0</v>
       </c>
-      <c r="D257" t="s">
+      <c r="D257" s="3" t="s">
         <v>984</v>
       </c>
       <c r="E257">
@@ -22224,7 +22231,7 @@
       <c r="C258">
         <v>0</v>
       </c>
-      <c r="D258" t="s">
+      <c r="D258" s="3" t="s">
         <v>984</v>
       </c>
       <c r="E258">
@@ -22295,7 +22302,7 @@
       <c r="C259">
         <v>0</v>
       </c>
-      <c r="D259" t="s">
+      <c r="D259" s="3" t="s">
         <v>1001</v>
       </c>
       <c r="E259">
@@ -22434,7 +22441,7 @@
       <c r="C261">
         <v>8427882</v>
       </c>
-      <c r="D261" t="s">
+      <c r="D261" s="3" t="s">
         <v>1057</v>
       </c>
       <c r="E261">
@@ -22505,7 +22512,7 @@
       <c r="C262">
         <v>0</v>
       </c>
-      <c r="D262" t="s">
+      <c r="D262" s="3" t="s">
         <v>1019</v>
       </c>
       <c r="E262">
@@ -22576,7 +22583,7 @@
       <c r="C263">
         <v>8302353</v>
       </c>
-      <c r="D263" t="s">
+      <c r="D263" s="3" t="s">
         <v>1027</v>
       </c>
       <c r="E263">
@@ -23002,7 +23009,7 @@
       <c r="C269">
         <v>2621661</v>
       </c>
-      <c r="D269" t="s">
+      <c r="D269" s="3" t="s">
         <v>960</v>
       </c>
       <c r="E269">
@@ -23073,7 +23080,7 @@
       <c r="C270">
         <v>0</v>
       </c>
-      <c r="D270" t="s">
+      <c r="D270" s="3" t="s">
         <v>980</v>
       </c>
       <c r="E270">
@@ -23144,7 +23151,7 @@
       <c r="C271">
         <v>0</v>
       </c>
-      <c r="D271" t="s">
+      <c r="D271" s="3" t="s">
         <v>979</v>
       </c>
       <c r="E271">
@@ -23286,7 +23293,7 @@
       <c r="C273">
         <v>2457391</v>
       </c>
-      <c r="D273" t="s">
+      <c r="D273" s="3" t="s">
         <v>936</v>
       </c>
       <c r="E273">
@@ -23354,7 +23361,7 @@
       <c r="C274">
         <v>0</v>
       </c>
-      <c r="D274" t="s">
+      <c r="D274" s="3" t="s">
         <v>975</v>
       </c>
       <c r="E274">
@@ -23425,7 +23432,7 @@
       <c r="C275">
         <v>2457391</v>
       </c>
-      <c r="D275" t="s">
+      <c r="D275" s="3" t="s">
         <v>936</v>
       </c>
       <c r="E275">
@@ -23493,7 +23500,7 @@
       <c r="C276">
         <v>2588614</v>
       </c>
-      <c r="D276" t="s">
+      <c r="D276" s="3" t="s">
         <v>910</v>
       </c>
       <c r="E276">
@@ -23564,7 +23571,7 @@
       <c r="C277">
         <v>9627066</v>
       </c>
-      <c r="D277" t="s">
+      <c r="D277" s="3" t="s">
         <v>176</v>
       </c>
       <c r="E277">
@@ -23703,7 +23710,7 @@
       <c r="C279">
         <v>0</v>
       </c>
-      <c r="D279" t="s">
+      <c r="D279" s="3" t="s">
         <v>973</v>
       </c>
       <c r="E279">
@@ -23774,7 +23781,7 @@
       <c r="C280">
         <v>9622955</v>
       </c>
-      <c r="D280" t="s">
+      <c r="D280" s="3" t="s">
         <v>176</v>
       </c>
       <c r="E280">
@@ -23845,7 +23852,7 @@
       <c r="C281">
         <v>9364648</v>
       </c>
-      <c r="D281" t="s">
+      <c r="D281" s="3" t="s">
         <v>460</v>
       </c>
       <c r="E281">
@@ -23916,7 +23923,7 @@
       <c r="C282">
         <v>9311720</v>
       </c>
-      <c r="D282" t="s">
+      <c r="D282" s="3" t="s">
         <v>967</v>
       </c>
       <c r="E282">
@@ -23984,7 +23991,7 @@
       <c r="C283">
         <v>2588614</v>
       </c>
-      <c r="D283" t="s">
+      <c r="D283" s="3" t="s">
         <v>910</v>
       </c>
       <c r="E283">
@@ -24055,7 +24062,7 @@
       <c r="C284">
         <v>2195433</v>
       </c>
-      <c r="D284" t="s">
+      <c r="D284" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E284">
@@ -24194,7 +24201,7 @@
       <c r="C286">
         <v>2474631</v>
       </c>
-      <c r="D286" t="s">
+      <c r="D286" s="3" t="s">
         <v>909</v>
       </c>
       <c r="E286">
@@ -24336,7 +24343,7 @@
       <c r="C288">
         <v>2621661</v>
       </c>
-      <c r="D288" t="s">
+      <c r="D288" s="3" t="s">
         <v>960</v>
       </c>
       <c r="E288">
@@ -24407,7 +24414,7 @@
       <c r="C289">
         <v>3768746</v>
       </c>
-      <c r="D289" t="s">
+      <c r="D289" s="3" t="s">
         <v>958</v>
       </c>
       <c r="E289">
@@ -24472,7 +24479,7 @@
       <c r="C290">
         <v>9278497</v>
       </c>
-      <c r="D290" t="s">
+      <c r="D290" s="3" t="s">
         <v>803</v>
       </c>
       <c r="E290">
@@ -24543,7 +24550,7 @@
       <c r="C291">
         <v>2466536</v>
       </c>
-      <c r="D291" t="s">
+      <c r="D291" s="3" t="s">
         <v>936</v>
       </c>
       <c r="E291">
@@ -24685,7 +24692,7 @@
       <c r="C293">
         <v>0</v>
       </c>
-      <c r="D293" t="s">
+      <c r="D293" s="3" t="s">
         <v>956</v>
       </c>
       <c r="E293">
@@ -24756,7 +24763,7 @@
       <c r="C294">
         <v>2820635</v>
       </c>
-      <c r="D294" t="s">
+      <c r="D294" s="3" t="s">
         <v>941</v>
       </c>
       <c r="E294">
@@ -24827,7 +24834,7 @@
       <c r="C295">
         <v>2509585</v>
       </c>
-      <c r="D295" t="s">
+      <c r="D295" s="3" t="s">
         <v>952</v>
       </c>
       <c r="E295">
@@ -24898,7 +24905,7 @@
       <c r="C296">
         <v>2762278</v>
       </c>
-      <c r="D296" t="s">
+      <c r="D296" s="3" t="s">
         <v>923</v>
       </c>
       <c r="E296">
@@ -24969,7 +24976,7 @@
       <c r="C297">
         <v>2723496</v>
       </c>
-      <c r="D297" t="s">
+      <c r="D297" s="3" t="s">
         <v>911</v>
       </c>
       <c r="E297">
@@ -25040,7 +25047,7 @@
       <c r="C298">
         <v>2583259</v>
       </c>
-      <c r="D298" t="s">
+      <c r="D298" s="3" t="s">
         <v>910</v>
       </c>
       <c r="E298">
@@ -25111,7 +25118,7 @@
       <c r="C299">
         <v>2478738</v>
       </c>
-      <c r="D299" t="s">
+      <c r="D299" s="3" t="s">
         <v>909</v>
       </c>
       <c r="E299">
@@ -25182,7 +25189,7 @@
       <c r="C300">
         <v>8051067</v>
       </c>
-      <c r="D300" t="s">
+      <c r="D300" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E300">
@@ -25253,7 +25260,7 @@
       <c r="C301">
         <v>7781005</v>
       </c>
-      <c r="D301" t="s">
+      <c r="D301" s="3" t="s">
         <v>943</v>
       </c>
       <c r="E301">
@@ -25324,7 +25331,7 @@
       <c r="C302">
         <v>2466536</v>
       </c>
-      <c r="D302" t="s">
+      <c r="D302" s="3" t="s">
         <v>936</v>
       </c>
       <c r="E302">
@@ -25395,7 +25402,7 @@
       <c r="C303">
         <v>2421117</v>
       </c>
-      <c r="D303" t="s">
+      <c r="D303" s="3" t="s">
         <v>908</v>
       </c>
       <c r="E303">
@@ -25466,7 +25473,7 @@
       <c r="C304">
         <v>2754972</v>
       </c>
-      <c r="D304" t="s">
+      <c r="D304" s="3" t="s">
         <v>923</v>
       </c>
       <c r="E304">
@@ -25537,7 +25544,7 @@
       <c r="C305">
         <v>2766046</v>
       </c>
-      <c r="D305" t="s">
+      <c r="D305" s="3" t="s">
         <v>591</v>
       </c>
       <c r="E305">
@@ -25608,7 +25615,7 @@
       <c r="C306">
         <v>2598802</v>
       </c>
-      <c r="D306" t="s">
+      <c r="D306" s="3" t="s">
         <v>910</v>
       </c>
       <c r="E306">
@@ -25679,7 +25686,7 @@
       <c r="C307">
         <v>2816267</v>
       </c>
-      <c r="D307" t="s">
+      <c r="D307" s="3" t="s">
         <v>941</v>
       </c>
       <c r="E307">
@@ -25747,7 +25754,7 @@
       <c r="C308">
         <v>2867605</v>
       </c>
-      <c r="D308" t="s">
+      <c r="D308" s="3" t="s">
         <v>564</v>
       </c>
       <c r="E308">
@@ -25818,7 +25825,7 @@
       <c r="C309">
         <v>2346352</v>
       </c>
-      <c r="D309" t="s">
+      <c r="D309" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E309">
@@ -25889,7 +25896,7 @@
       <c r="C310">
         <v>9924868</v>
       </c>
-      <c r="D310" t="s">
+      <c r="D310" s="3" t="s">
         <v>320</v>
       </c>
       <c r="E310">
@@ -25960,7 +25967,7 @@
       <c r="C311">
         <v>9781342</v>
       </c>
-      <c r="D311" t="s">
+      <c r="D311" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E311">
@@ -26031,7 +26038,7 @@
       <c r="C312">
         <v>2414600</v>
       </c>
-      <c r="D312" t="s">
+      <c r="D312" s="3" t="s">
         <v>908</v>
       </c>
       <c r="E312">
@@ -26102,7 +26109,7 @@
       <c r="C313">
         <v>2723142</v>
       </c>
-      <c r="D313" t="s">
+      <c r="D313" s="3" t="s">
         <v>911</v>
       </c>
       <c r="E313">
@@ -26173,7 +26180,7 @@
       <c r="C314">
         <v>2598806</v>
       </c>
-      <c r="D314" t="s">
+      <c r="D314" s="3" t="s">
         <v>910</v>
       </c>
       <c r="E314">
@@ -26244,7 +26251,7 @@
       <c r="C315">
         <v>2598802</v>
       </c>
-      <c r="D315" t="s">
+      <c r="D315" s="3" t="s">
         <v>910</v>
       </c>
       <c r="E315">
@@ -26315,7 +26322,7 @@
       <c r="C316">
         <v>2747622</v>
       </c>
-      <c r="D316" t="s">
+      <c r="D316" s="3" t="s">
         <v>923</v>
       </c>
       <c r="E316">
@@ -26386,7 +26393,7 @@
       <c r="C317">
         <v>9247369</v>
       </c>
-      <c r="D317" t="s">
+      <c r="D317" s="3" t="s">
         <v>856</v>
       </c>
       <c r="E317">
@@ -26457,7 +26464,7 @@
       <c r="C318">
         <v>2459922</v>
       </c>
-      <c r="D318" t="s">
+      <c r="D318" s="3" t="s">
         <v>936</v>
       </c>
       <c r="E318">
@@ -26528,7 +26535,7 @@
       <c r="C319">
         <v>7924459</v>
       </c>
-      <c r="D319" t="s">
+      <c r="D319" s="3" t="s">
         <v>929</v>
       </c>
       <c r="E319">
@@ -26599,7 +26606,7 @@
       <c r="C320">
         <v>8049784</v>
       </c>
-      <c r="D320" t="s">
+      <c r="D320" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E320">
@@ -26670,7 +26677,7 @@
       <c r="C321">
         <v>2700619</v>
       </c>
-      <c r="D321" t="s">
+      <c r="D321" s="3" t="s">
         <v>913</v>
       </c>
       <c r="E321">
@@ -26741,7 +26748,7 @@
       <c r="C322">
         <v>2543052</v>
       </c>
-      <c r="D322" t="s">
+      <c r="D322" s="3" t="s">
         <v>937</v>
       </c>
       <c r="E322">
@@ -26812,7 +26819,7 @@
       <c r="C323">
         <v>9424029</v>
       </c>
-      <c r="D323" t="s">
+      <c r="D323" s="3" t="s">
         <v>420</v>
       </c>
       <c r="E323">
@@ -26883,7 +26890,7 @@
       <c r="C324">
         <v>9247854</v>
       </c>
-      <c r="D324" t="s">
+      <c r="D324" s="3" t="s">
         <v>856</v>
       </c>
       <c r="E324">
@@ -26954,7 +26961,7 @@
       <c r="C325">
         <v>7711902</v>
       </c>
-      <c r="D325" t="s">
+      <c r="D325" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E325">
@@ -27025,7 +27032,7 @@
       <c r="C326">
         <v>2767487</v>
       </c>
-      <c r="D326" t="s">
+      <c r="D326" s="3" t="s">
         <v>591</v>
       </c>
       <c r="E326">
@@ -27096,7 +27103,7 @@
       <c r="C327">
         <v>2488598</v>
       </c>
-      <c r="D327" t="s">
+      <c r="D327" s="3" t="s">
         <v>909</v>
       </c>
       <c r="E327">
@@ -27167,7 +27174,7 @@
       <c r="C328">
         <v>2195433</v>
       </c>
-      <c r="D328" t="s">
+      <c r="D328" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E328">
@@ -27238,7 +27245,7 @@
       <c r="C329">
         <v>9344974</v>
       </c>
-      <c r="D329" t="s">
+      <c r="D329" s="3" t="s">
         <v>906</v>
       </c>
       <c r="E329">
@@ -27309,7 +27316,7 @@
       <c r="C330">
         <v>2598563</v>
       </c>
-      <c r="D330" t="s">
+      <c r="D330" s="3" t="s">
         <v>910</v>
       </c>
       <c r="E330">
@@ -27380,7 +27387,7 @@
       <c r="C331">
         <v>2629768</v>
       </c>
-      <c r="D331" t="s">
+      <c r="D331" s="3" t="s">
         <v>938</v>
       </c>
       <c r="E331">
@@ -27451,7 +27458,7 @@
       <c r="C332">
         <v>2724579</v>
       </c>
-      <c r="D332" t="s">
+      <c r="D332" s="3" t="s">
         <v>911</v>
       </c>
       <c r="E332">
@@ -27522,7 +27529,7 @@
       <c r="C333">
         <v>2766046</v>
       </c>
-      <c r="D333" t="s">
+      <c r="D333" s="3" t="s">
         <v>591</v>
       </c>
       <c r="E333">
@@ -27593,7 +27600,7 @@
       <c r="C334">
         <v>3876389</v>
       </c>
-      <c r="D334" t="s">
+      <c r="D334" s="3" t="s">
         <v>904</v>
       </c>
       <c r="E334">
@@ -27658,7 +27665,7 @@
       <c r="C335">
         <v>9579607</v>
       </c>
-      <c r="D335" t="s">
+      <c r="D335" s="3" t="s">
         <v>204</v>
       </c>
       <c r="E335">
@@ -27729,7 +27736,7 @@
       <c r="C336">
         <v>9542170</v>
       </c>
-      <c r="D336" t="s">
+      <c r="D336" s="3" t="s">
         <v>549</v>
       </c>
       <c r="E336">
@@ -27800,7 +27807,7 @@
       <c r="C337">
         <v>9781347</v>
       </c>
-      <c r="D337" t="s">
+      <c r="D337" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E337">
@@ -27871,7 +27878,7 @@
       <c r="C338">
         <v>9261048</v>
       </c>
-      <c r="D338" t="s">
+      <c r="D338" s="3" t="s">
         <v>803</v>
       </c>
       <c r="E338">
@@ -27942,7 +27949,7 @@
       <c r="C339">
         <v>2012517</v>
       </c>
-      <c r="D339" t="s">
+      <c r="D339" s="3" t="s">
         <v>373</v>
       </c>
       <c r="E339">
@@ -28013,7 +28020,7 @@
       <c r="C340">
         <v>9773051</v>
       </c>
-      <c r="D340" t="s">
+      <c r="D340" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E340">
@@ -28084,7 +28091,7 @@
       <c r="C341">
         <v>2195433</v>
       </c>
-      <c r="D341" t="s">
+      <c r="D341" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E341">
@@ -28155,7 +28162,7 @@
       <c r="C342">
         <v>9610075</v>
       </c>
-      <c r="D342" t="s">
+      <c r="D342" s="3" t="s">
         <v>176</v>
       </c>
       <c r="E342">
@@ -28226,7 +28233,7 @@
       <c r="C343">
         <v>9774063</v>
       </c>
-      <c r="D343" t="s">
+      <c r="D343" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E343">
@@ -28297,7 +28304,7 @@
       <c r="C344">
         <v>4738406</v>
       </c>
-      <c r="D344" t="s">
+      <c r="D344" s="3" t="s">
         <v>878</v>
       </c>
       <c r="E344">
@@ -28365,7 +28372,7 @@
       <c r="C345">
         <v>3835909</v>
       </c>
-      <c r="D345" t="s">
+      <c r="D345" s="3" t="s">
         <v>385</v>
       </c>
       <c r="E345">
@@ -28430,7 +28437,7 @@
       <c r="C346">
         <v>3834747</v>
       </c>
-      <c r="D346" t="s">
+      <c r="D346" s="3" t="s">
         <v>385</v>
       </c>
       <c r="E346">
@@ -28495,7 +28502,7 @@
       <c r="C347">
         <v>3864874</v>
       </c>
-      <c r="D347" t="s">
+      <c r="D347" s="3" t="s">
         <v>889</v>
       </c>
       <c r="E347">
@@ -28560,7 +28567,7 @@
       <c r="C348">
         <v>3861656</v>
       </c>
-      <c r="D348" t="s">
+      <c r="D348" s="3" t="s">
         <v>889</v>
       </c>
       <c r="E348">
@@ -28693,7 +28700,7 @@
       <c r="C350">
         <v>3652773</v>
       </c>
-      <c r="D350" t="s">
+      <c r="D350" s="3" t="s">
         <v>670</v>
       </c>
       <c r="E350">
@@ -28758,7 +28765,7 @@
       <c r="C351">
         <v>3652773</v>
       </c>
-      <c r="D351" t="s">
+      <c r="D351" s="3" t="s">
         <v>670</v>
       </c>
       <c r="E351">
@@ -28823,7 +28830,7 @@
       <c r="C352">
         <v>3716294</v>
       </c>
-      <c r="D352" t="s">
+      <c r="D352" s="3" t="s">
         <v>859</v>
       </c>
       <c r="E352">
@@ -28888,7 +28895,7 @@
       <c r="C353">
         <v>3727257</v>
       </c>
-      <c r="D353" t="s">
+      <c r="D353" s="3" t="s">
         <v>859</v>
       </c>
       <c r="E353">
@@ -28953,7 +28960,7 @@
       <c r="C354">
         <v>4835136</v>
       </c>
-      <c r="D354" t="s">
+      <c r="D354" s="3" t="s">
         <v>872</v>
       </c>
       <c r="E354">
@@ -29021,7 +29028,7 @@
       <c r="C355">
         <v>9627066</v>
       </c>
-      <c r="D355" t="s">
+      <c r="D355" s="3" t="s">
         <v>176</v>
       </c>
       <c r="E355">
@@ -29092,7 +29099,7 @@
       <c r="C356">
         <v>4829078</v>
       </c>
-      <c r="D356" t="s">
+      <c r="D356" s="3" t="s">
         <v>872</v>
       </c>
       <c r="E356">
@@ -29302,7 +29309,7 @@
       <c r="C359">
         <v>4790487</v>
       </c>
-      <c r="D359" t="s">
+      <c r="D359" s="3" t="s">
         <v>862</v>
       </c>
       <c r="E359">
@@ -29370,7 +29377,7 @@
       <c r="C360">
         <v>9261048</v>
       </c>
-      <c r="D360" t="s">
+      <c r="D360" s="3" t="s">
         <v>803</v>
       </c>
       <c r="E360">
@@ -29441,7 +29448,7 @@
       <c r="C361">
         <v>4790487</v>
       </c>
-      <c r="D361" t="s">
+      <c r="D361" s="3" t="s">
         <v>862</v>
       </c>
       <c r="E361">
@@ -29509,7 +29516,7 @@
       <c r="C362">
         <v>9390257</v>
       </c>
-      <c r="D362" t="s">
+      <c r="D362" s="3" t="s">
         <v>279</v>
       </c>
       <c r="E362">
@@ -29580,7 +29587,7 @@
       <c r="C363">
         <v>3726800</v>
       </c>
-      <c r="D363" t="s">
+      <c r="D363" s="3" t="s">
         <v>859</v>
       </c>
       <c r="E363">
@@ -29645,7 +29652,7 @@
       <c r="C364">
         <v>4771355</v>
       </c>
-      <c r="D364" t="s">
+      <c r="D364" s="3" t="s">
         <v>812</v>
       </c>
       <c r="E364">
@@ -29855,7 +29862,7 @@
       <c r="C367">
         <v>4771355</v>
       </c>
-      <c r="D367" t="s">
+      <c r="D367" s="3" t="s">
         <v>812</v>
       </c>
       <c r="E367">
@@ -29923,7 +29930,7 @@
       <c r="C368">
         <v>9390257</v>
       </c>
-      <c r="D368" t="s">
+      <c r="D368" s="3" t="s">
         <v>279</v>
       </c>
       <c r="E368">
@@ -29994,7 +30001,7 @@
       <c r="C369">
         <v>9246219</v>
       </c>
-      <c r="D369" t="s">
+      <c r="D369" s="3" t="s">
         <v>856</v>
       </c>
       <c r="E369">
@@ -30065,7 +30072,7 @@
       <c r="C370">
         <v>8109303</v>
       </c>
-      <c r="D370" t="s">
+      <c r="D370" s="3" t="s">
         <v>156</v>
       </c>
       <c r="E370">
@@ -30136,7 +30143,7 @@
       <c r="C371">
         <v>8048836</v>
       </c>
-      <c r="D371" t="s">
+      <c r="D371" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E371">
@@ -30207,7 +30214,7 @@
       <c r="C372">
         <v>8048836</v>
       </c>
-      <c r="D372" t="s">
+      <c r="D372" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E372">
@@ -30278,7 +30285,7 @@
       <c r="C373">
         <v>8048836</v>
       </c>
-      <c r="D373" t="s">
+      <c r="D373" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E373">
@@ -30349,7 +30356,7 @@
       <c r="C374">
         <v>9887783</v>
       </c>
-      <c r="D374" t="s">
+      <c r="D374" s="3" t="s">
         <v>94</v>
       </c>
       <c r="E374">
@@ -30420,7 +30427,7 @@
       <c r="C375">
         <v>9911762</v>
       </c>
-      <c r="D375" t="s">
+      <c r="D375" s="3" t="s">
         <v>320</v>
       </c>
       <c r="E375">
@@ -30491,7 +30498,7 @@
       <c r="C376">
         <v>2048035</v>
       </c>
-      <c r="D376" t="s">
+      <c r="D376" s="3" t="s">
         <v>608</v>
       </c>
       <c r="E376">
@@ -30562,7 +30569,7 @@
       <c r="C377">
         <v>7611321</v>
       </c>
-      <c r="D377" t="s">
+      <c r="D377" s="3" t="s">
         <v>84</v>
       </c>
       <c r="E377">
@@ -30633,7 +30640,7 @@
       <c r="C378">
         <v>7611343</v>
       </c>
-      <c r="D378" t="s">
+      <c r="D378" s="3" t="s">
         <v>84</v>
       </c>
       <c r="E378">
@@ -30704,7 +30711,7 @@
       <c r="C379">
         <v>7659317</v>
       </c>
-      <c r="D379" t="s">
+      <c r="D379" s="3" t="s">
         <v>248</v>
       </c>
       <c r="E379">
@@ -30775,7 +30782,7 @@
       <c r="C380">
         <v>4710399</v>
       </c>
-      <c r="D380" t="s">
+      <c r="D380" s="3" t="s">
         <v>829</v>
       </c>
       <c r="E380">
@@ -30843,7 +30850,7 @@
       <c r="C381">
         <v>4541386</v>
       </c>
-      <c r="D381" t="s">
+      <c r="D381" s="3" t="s">
         <v>745</v>
       </c>
       <c r="E381">
@@ -30911,7 +30918,7 @@
       <c r="C382">
         <v>4541386</v>
       </c>
-      <c r="D382" t="s">
+      <c r="D382" s="3" t="s">
         <v>745</v>
       </c>
       <c r="E382">
@@ -30979,7 +30986,7 @@
       <c r="C383">
         <v>4541386</v>
       </c>
-      <c r="D383" t="s">
+      <c r="D383" s="3" t="s">
         <v>745</v>
       </c>
       <c r="E383">
@@ -31047,7 +31054,7 @@
       <c r="C384">
         <v>9278497</v>
       </c>
-      <c r="D384" t="s">
+      <c r="D384" s="3" t="s">
         <v>803</v>
       </c>
       <c r="E384">
@@ -31118,7 +31125,7 @@
       <c r="C385">
         <v>7865361</v>
       </c>
-      <c r="D385" t="s">
+      <c r="D385" s="3" t="s">
         <v>790</v>
       </c>
       <c r="E385">
@@ -31189,7 +31196,7 @@
       <c r="C386">
         <v>4731963</v>
       </c>
-      <c r="D386" t="s">
+      <c r="D386" s="3" t="s">
         <v>839</v>
       </c>
       <c r="E386">
@@ -31257,7 +31264,7 @@
       <c r="C387">
         <v>9795641</v>
       </c>
-      <c r="D387" t="s">
+      <c r="D387" s="3" t="s">
         <v>761</v>
       </c>
       <c r="E387">
@@ -31328,7 +31335,7 @@
       <c r="C388">
         <v>0</v>
       </c>
-      <c r="D388" t="s">
+      <c r="D388" s="3" t="s">
         <v>644</v>
       </c>
       <c r="E388">
@@ -31399,7 +31406,7 @@
       <c r="C389">
         <v>0</v>
       </c>
-      <c r="D389" t="s">
+      <c r="D389" s="3" t="s">
         <v>657</v>
       </c>
       <c r="E389">
@@ -31470,7 +31477,7 @@
       <c r="C390">
         <v>0</v>
       </c>
-      <c r="D390" t="s">
+      <c r="D390" s="3" t="s">
         <v>819</v>
       </c>
       <c r="E390">
@@ -31612,7 +31619,7 @@
       <c r="C392">
         <v>0</v>
       </c>
-      <c r="D392" t="s">
+      <c r="D392" s="3" t="s">
         <v>828</v>
       </c>
       <c r="E392">
@@ -31683,7 +31690,7 @@
       <c r="C393">
         <v>7714965</v>
       </c>
-      <c r="D393" t="s">
+      <c r="D393" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E393">
@@ -31754,7 +31761,7 @@
       <c r="C394">
         <v>7715481</v>
       </c>
-      <c r="D394" t="s">
+      <c r="D394" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E394">
@@ -31967,7 +31974,7 @@
       <c r="C397">
         <v>9178332</v>
       </c>
-      <c r="D397" t="s">
+      <c r="D397" s="3" t="s">
         <v>738</v>
       </c>
       <c r="E397">
@@ -32180,7 +32187,7 @@
       <c r="C400">
         <v>9178332</v>
       </c>
-      <c r="D400" t="s">
+      <c r="D400" s="3" t="s">
         <v>738</v>
       </c>
       <c r="E400">
@@ -32251,7 +32258,7 @@
       <c r="C401">
         <v>7664621</v>
       </c>
-      <c r="D401" t="s">
+      <c r="D401" s="3" t="s">
         <v>793</v>
       </c>
       <c r="E401">
@@ -32393,7 +32400,7 @@
       <c r="C403">
         <v>7969289</v>
       </c>
-      <c r="D403" t="s">
+      <c r="D403" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E403">
@@ -32464,7 +32471,7 @@
       <c r="C404">
         <v>7971104</v>
       </c>
-      <c r="D404" t="s">
+      <c r="D404" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E404">
@@ -32535,7 +32542,7 @@
       <c r="C405">
         <v>7965831</v>
       </c>
-      <c r="D405" t="s">
+      <c r="D405" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E405">
@@ -32606,7 +32613,7 @@
       <c r="C406">
         <v>7967800</v>
       </c>
-      <c r="D406" t="s">
+      <c r="D406" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E406">
@@ -32748,7 +32755,7 @@
       <c r="C408">
         <v>7841266</v>
       </c>
-      <c r="D408" t="s">
+      <c r="D408" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E408">
@@ -32961,7 +32968,7 @@
       <c r="C411">
         <v>2324132</v>
       </c>
-      <c r="D411" t="s">
+      <c r="D411" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E411">
@@ -33032,7 +33039,7 @@
       <c r="C412">
         <v>9612557</v>
       </c>
-      <c r="D412" t="s">
+      <c r="D412" s="3" t="s">
         <v>176</v>
       </c>
       <c r="E412">
@@ -33103,7 +33110,7 @@
       <c r="C413">
         <v>9689331</v>
       </c>
-      <c r="D413" t="s">
+      <c r="D413" s="3" t="s">
         <v>277</v>
       </c>
       <c r="E413">
@@ -33174,7 +33181,7 @@
       <c r="C414">
         <v>7701040</v>
       </c>
-      <c r="D414" t="s">
+      <c r="D414" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E414">
@@ -33245,7 +33252,7 @@
       <c r="C415">
         <v>9627066</v>
       </c>
-      <c r="D415" t="s">
+      <c r="D415" s="3" t="s">
         <v>176</v>
       </c>
       <c r="E415">
@@ -33316,7 +33323,7 @@
       <c r="C416">
         <v>9070578</v>
       </c>
-      <c r="D416" t="s">
+      <c r="D416" s="3" t="s">
         <v>725</v>
       </c>
       <c r="E416">
@@ -33387,7 +33394,7 @@
       <c r="C417">
         <v>9578162</v>
       </c>
-      <c r="D417" t="s">
+      <c r="D417" s="3" t="s">
         <v>204</v>
       </c>
       <c r="E417">
@@ -33458,7 +33465,7 @@
       <c r="C418">
         <v>9261048</v>
       </c>
-      <c r="D418" t="s">
+      <c r="D418" s="3" t="s">
         <v>803</v>
       </c>
       <c r="E418">
@@ -33529,7 +33536,7 @@
       <c r="C419">
         <v>2195433</v>
       </c>
-      <c r="D419" t="s">
+      <c r="D419" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E419">
@@ -33600,7 +33607,7 @@
       <c r="C420">
         <v>2251440</v>
       </c>
-      <c r="D420" t="s">
+      <c r="D420" s="3" t="s">
         <v>309</v>
       </c>
       <c r="E420">
@@ -33955,7 +33962,7 @@
       <c r="C425">
         <v>9730948</v>
       </c>
-      <c r="D425" t="s">
+      <c r="D425" s="3" t="s">
         <v>451</v>
       </c>
       <c r="E425">
@@ -34026,7 +34033,7 @@
       <c r="C426">
         <v>9411631</v>
       </c>
-      <c r="D426" t="s">
+      <c r="D426" s="3" t="s">
         <v>238</v>
       </c>
       <c r="E426">
@@ -34097,7 +34104,7 @@
       <c r="C427">
         <v>8000193</v>
       </c>
-      <c r="D427" t="s">
+      <c r="D427" s="3" t="s">
         <v>841</v>
       </c>
       <c r="E427">
@@ -34168,7 +34175,7 @@
       <c r="C428">
         <v>8000193</v>
       </c>
-      <c r="D428" t="s">
+      <c r="D428" s="3" t="s">
         <v>841</v>
       </c>
       <c r="E428">
@@ -34239,7 +34246,7 @@
       <c r="C429">
         <v>7857993</v>
       </c>
-      <c r="D429" t="s">
+      <c r="D429" s="3" t="s">
         <v>790</v>
       </c>
       <c r="E429">
@@ -34310,7 +34317,7 @@
       <c r="C430">
         <v>9074490</v>
       </c>
-      <c r="D430" t="s">
+      <c r="D430" s="3" t="s">
         <v>725</v>
       </c>
       <c r="E430">
@@ -34381,7 +34388,7 @@
       <c r="C431">
         <v>4482042</v>
       </c>
-      <c r="D431" t="s">
+      <c r="D431" s="3" t="s">
         <v>64</v>
       </c>
       <c r="E431">
@@ -34449,7 +34456,7 @@
       <c r="C432">
         <v>9136276</v>
       </c>
-      <c r="D432" t="s">
+      <c r="D432" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E432">
@@ -34520,7 +34527,7 @@
       <c r="C433">
         <v>9136276</v>
       </c>
-      <c r="D433" t="s">
+      <c r="D433" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E433">
@@ -34591,7 +34598,7 @@
       <c r="C434">
         <v>9136276</v>
       </c>
-      <c r="D434" t="s">
+      <c r="D434" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E434">
@@ -34662,7 +34669,7 @@
       <c r="C435">
         <v>9136276</v>
       </c>
-      <c r="D435" t="s">
+      <c r="D435" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E435">
@@ -34733,7 +34740,7 @@
       <c r="C436">
         <v>9136276</v>
       </c>
-      <c r="D436" t="s">
+      <c r="D436" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E436">
@@ -34875,7 +34882,7 @@
       <c r="C438">
         <v>9136276</v>
       </c>
-      <c r="D438" t="s">
+      <c r="D438" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E438">
@@ -34946,7 +34953,7 @@
       <c r="C439">
         <v>9150942</v>
       </c>
-      <c r="D439" t="s">
+      <c r="D439" s="3" t="s">
         <v>734</v>
       </c>
       <c r="E439">
@@ -35017,7 +35024,7 @@
       <c r="C440">
         <v>4645295</v>
       </c>
-      <c r="D440" t="s">
+      <c r="D440" s="3" t="s">
         <v>752</v>
       </c>
       <c r="E440">
@@ -35085,7 +35092,7 @@
       <c r="C441">
         <v>4600800</v>
       </c>
-      <c r="D441" t="s">
+      <c r="D441" s="3" t="s">
         <v>775</v>
       </c>
       <c r="E441">
@@ -35153,7 +35160,7 @@
       <c r="C442">
         <v>4600800</v>
       </c>
-      <c r="D442" t="s">
+      <c r="D442" s="3" t="s">
         <v>775</v>
       </c>
       <c r="E442">
@@ -35221,7 +35228,7 @@
       <c r="C443">
         <v>4668892</v>
       </c>
-      <c r="D443" t="s">
+      <c r="D443" s="3" t="s">
         <v>822</v>
       </c>
       <c r="E443">
@@ -35289,7 +35296,7 @@
       <c r="C444">
         <v>4629919</v>
       </c>
-      <c r="D444" t="s">
+      <c r="D444" s="3" t="s">
         <v>773</v>
       </c>
       <c r="E444">
@@ -35357,7 +35364,7 @@
       <c r="C445">
         <v>4559485</v>
       </c>
-      <c r="D445" t="s">
+      <c r="D445" s="3" t="s">
         <v>427</v>
       </c>
       <c r="E445">
@@ -35425,7 +35432,7 @@
       <c r="C446">
         <v>4517810</v>
       </c>
-      <c r="D446" t="s">
+      <c r="D446" s="3" t="s">
         <v>403</v>
       </c>
       <c r="E446">
@@ -35493,7 +35500,7 @@
       <c r="C447">
         <v>4517930</v>
       </c>
-      <c r="D447" t="s">
+      <c r="D447" s="3" t="s">
         <v>403</v>
       </c>
       <c r="E447">
@@ -35561,7 +35568,7 @@
       <c r="C448">
         <v>4628318</v>
       </c>
-      <c r="D448" t="s">
+      <c r="D448" s="3" t="s">
         <v>773</v>
       </c>
       <c r="E448">
@@ -35629,7 +35636,7 @@
       <c r="C449">
         <v>4561585</v>
       </c>
-      <c r="D449" t="s">
+      <c r="D449" s="3" t="s">
         <v>427</v>
       </c>
       <c r="E449">
@@ -35697,7 +35704,7 @@
       <c r="C450">
         <v>0</v>
       </c>
-      <c r="D450" t="s">
+      <c r="D450" s="3" t="s">
         <v>683</v>
       </c>
       <c r="E450">
@@ -35768,7 +35775,7 @@
       <c r="C451">
         <v>0</v>
       </c>
-      <c r="D451" t="s">
+      <c r="D451" s="3" t="s">
         <v>640</v>
       </c>
       <c r="E451">
@@ -35839,7 +35846,7 @@
       <c r="C452">
         <v>0</v>
       </c>
-      <c r="D452" t="s">
+      <c r="D452" s="3" t="s">
         <v>640</v>
       </c>
       <c r="E452">
@@ -35981,7 +35988,7 @@
       <c r="C454">
         <v>9096947</v>
       </c>
-      <c r="D454" t="s">
+      <c r="D454" s="3" t="s">
         <v>727</v>
       </c>
       <c r="E454">
@@ -36052,7 +36059,7 @@
       <c r="C455">
         <v>8014588</v>
       </c>
-      <c r="D455" t="s">
+      <c r="D455" s="3" t="s">
         <v>847</v>
       </c>
       <c r="E455">
@@ -36123,7 +36130,7 @@
       <c r="C456">
         <v>4771355</v>
       </c>
-      <c r="D456" t="s">
+      <c r="D456" s="3" t="s">
         <v>812</v>
       </c>
       <c r="E456">
@@ -36191,7 +36198,7 @@
       <c r="C457">
         <v>4771355</v>
       </c>
-      <c r="D457" t="s">
+      <c r="D457" s="3" t="s">
         <v>812</v>
       </c>
       <c r="E457">
@@ -36259,7 +36266,7 @@
       <c r="C458">
         <v>4553435</v>
       </c>
-      <c r="D458" t="s">
+      <c r="D458" s="3" t="s">
         <v>427</v>
       </c>
       <c r="E458">
@@ -36327,7 +36334,7 @@
       <c r="C459">
         <v>4695461</v>
       </c>
-      <c r="D459" t="s">
+      <c r="D459" s="3" t="s">
         <v>829</v>
       </c>
       <c r="E459">
@@ -36395,7 +36402,7 @@
       <c r="C460">
         <v>8954678</v>
       </c>
-      <c r="D460" t="s">
+      <c r="D460" s="3" t="s">
         <v>723</v>
       </c>
       <c r="E460">
@@ -36466,7 +36473,7 @@
       <c r="C461">
         <v>8898854</v>
       </c>
-      <c r="D461" t="s">
+      <c r="D461" s="3" t="s">
         <v>717</v>
       </c>
       <c r="E461">
@@ -36537,7 +36544,7 @@
       <c r="C462">
         <v>0</v>
       </c>
-      <c r="D462" t="s">
+      <c r="D462" s="3" t="s">
         <v>640</v>
       </c>
       <c r="E462">
@@ -36608,7 +36615,7 @@
       <c r="C463">
         <v>8798048</v>
       </c>
-      <c r="D463" t="s">
+      <c r="D463" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E463">
@@ -36679,7 +36686,7 @@
       <c r="C464">
         <v>9142958</v>
       </c>
-      <c r="D464" t="s">
+      <c r="D464" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E464">
@@ -36750,7 +36757,7 @@
       <c r="C465">
         <v>9142958</v>
       </c>
-      <c r="D465" t="s">
+      <c r="D465" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E465">
@@ -36892,7 +36899,7 @@
       <c r="C467">
         <v>4245207</v>
       </c>
-      <c r="D467" t="s">
+      <c r="D467" s="3" t="s">
         <v>418</v>
       </c>
       <c r="E467">
@@ -36960,7 +36967,7 @@
       <c r="C468">
         <v>4242854</v>
       </c>
-      <c r="D468" t="s">
+      <c r="D468" s="3" t="s">
         <v>418</v>
       </c>
       <c r="E468">
@@ -37028,7 +37035,7 @@
       <c r="C469">
         <v>8933029</v>
       </c>
-      <c r="D469" t="s">
+      <c r="D469" s="3" t="s">
         <v>691</v>
       </c>
       <c r="E469">
@@ -37099,7 +37106,7 @@
       <c r="C470">
         <v>9434598</v>
       </c>
-      <c r="D470" t="s">
+      <c r="D470" s="3" t="s">
         <v>420</v>
       </c>
       <c r="E470">
@@ -37170,7 +37177,7 @@
       <c r="C471">
         <v>9434598</v>
       </c>
-      <c r="D471" t="s">
+      <c r="D471" s="3" t="s">
         <v>420</v>
       </c>
       <c r="E471">
@@ -37241,7 +37248,7 @@
       <c r="C472">
         <v>9437196</v>
       </c>
-      <c r="D472" t="s">
+      <c r="D472" s="3" t="s">
         <v>420</v>
       </c>
       <c r="E472">
@@ -37312,7 +37319,7 @@
       <c r="C473">
         <v>0</v>
       </c>
-      <c r="D473" t="s">
+      <c r="D473" s="3" t="s">
         <v>640</v>
       </c>
       <c r="E473">
@@ -37383,7 +37390,7 @@
       <c r="C474">
         <v>9128822</v>
       </c>
-      <c r="D474" t="s">
+      <c r="D474" s="3" t="s">
         <v>686</v>
       </c>
       <c r="E474">
@@ -37454,7 +37461,7 @@
       <c r="C475">
         <v>4239228</v>
       </c>
-      <c r="D475" t="s">
+      <c r="D475" s="3" t="s">
         <v>675</v>
       </c>
       <c r="E475">
@@ -37522,7 +37529,7 @@
       <c r="C476">
         <v>0</v>
       </c>
-      <c r="D476" t="s">
+      <c r="D476" s="3" t="s">
         <v>683</v>
       </c>
       <c r="E476">
@@ -37593,7 +37600,7 @@
       <c r="C477">
         <v>0</v>
       </c>
-      <c r="D477" t="s">
+      <c r="D477" s="3" t="s">
         <v>644</v>
       </c>
       <c r="E477">
@@ -37664,7 +37671,7 @@
       <c r="C478">
         <v>4312505</v>
       </c>
-      <c r="D478" t="s">
+      <c r="D478" s="3" t="s">
         <v>639</v>
       </c>
       <c r="E478">
@@ -37732,7 +37739,7 @@
       <c r="C479">
         <v>9927975</v>
       </c>
-      <c r="D479" t="s">
+      <c r="D479" s="3" t="s">
         <v>320</v>
       </c>
       <c r="E479">
@@ -37803,7 +37810,7 @@
       <c r="C480">
         <v>0</v>
       </c>
-      <c r="D480" t="s">
+      <c r="D480" s="3" t="s">
         <v>657</v>
       </c>
       <c r="E480">
@@ -37874,7 +37881,7 @@
       <c r="C481">
         <v>3649241</v>
       </c>
-      <c r="D481" t="s">
+      <c r="D481" s="3" t="s">
         <v>670</v>
       </c>
       <c r="E481">
@@ -38010,7 +38017,7 @@
       <c r="C483">
         <v>3711039</v>
       </c>
-      <c r="D483" t="s">
+      <c r="D483" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E483">
@@ -38075,7 +38082,7 @@
       <c r="C484">
         <v>3711039</v>
       </c>
-      <c r="D484" t="s">
+      <c r="D484" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E484">
@@ -38140,7 +38147,7 @@
       <c r="C485">
         <v>3711039</v>
       </c>
-      <c r="D485" t="s">
+      <c r="D485" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E485">
@@ -38347,7 +38354,7 @@
       <c r="C488">
         <v>0</v>
       </c>
-      <c r="D488" t="s">
+      <c r="D488" s="3" t="s">
         <v>657</v>
       </c>
       <c r="E488">
@@ -38418,7 +38425,7 @@
       <c r="C489">
         <v>7876555</v>
       </c>
-      <c r="D489" t="s">
+      <c r="D489" s="3" t="s">
         <v>324</v>
       </c>
       <c r="E489">
@@ -38489,7 +38496,7 @@
       <c r="C490">
         <v>7876555</v>
       </c>
-      <c r="D490" t="s">
+      <c r="D490" s="3" t="s">
         <v>324</v>
       </c>
       <c r="E490">
@@ -38560,7 +38567,7 @@
       <c r="C491">
         <v>7876555</v>
       </c>
-      <c r="D491" t="s">
+      <c r="D491" s="3" t="s">
         <v>324</v>
       </c>
       <c r="E491">
@@ -38631,7 +38638,7 @@
       <c r="C492">
         <v>7876555</v>
       </c>
-      <c r="D492" t="s">
+      <c r="D492" s="3" t="s">
         <v>324</v>
       </c>
       <c r="E492">
@@ -38702,7 +38709,7 @@
       <c r="C493">
         <v>3711039</v>
       </c>
-      <c r="D493" t="s">
+      <c r="D493" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E493">
@@ -38767,7 +38774,7 @@
       <c r="C494">
         <v>3711039</v>
       </c>
-      <c r="D494" t="s">
+      <c r="D494" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E494">
@@ -38832,7 +38839,7 @@
       <c r="C495">
         <v>3711039</v>
       </c>
-      <c r="D495" t="s">
+      <c r="D495" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E495">
@@ -38897,7 +38904,7 @@
       <c r="C496">
         <v>3711039</v>
       </c>
-      <c r="D496" t="s">
+      <c r="D496" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E496">
@@ -38962,7 +38969,7 @@
       <c r="C497">
         <v>3711039</v>
       </c>
-      <c r="D497" t="s">
+      <c r="D497" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E497">
@@ -39027,7 +39034,7 @@
       <c r="C498">
         <v>3711039</v>
       </c>
-      <c r="D498" t="s">
+      <c r="D498" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E498">
@@ -39092,7 +39099,7 @@
       <c r="C499">
         <v>3711039</v>
       </c>
-      <c r="D499" t="s">
+      <c r="D499" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E499">
@@ -39157,7 +39164,7 @@
       <c r="C500">
         <v>3711039</v>
       </c>
-      <c r="D500" t="s">
+      <c r="D500" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E500">
@@ -39222,7 +39229,7 @@
       <c r="C501">
         <v>3711039</v>
       </c>
-      <c r="D501" t="s">
+      <c r="D501" s="3" t="s">
         <v>667</v>
       </c>
       <c r="E501">
@@ -39287,7 +39294,7 @@
       <c r="C502">
         <v>3647775</v>
       </c>
-      <c r="D502" t="s">
+      <c r="D502" s="3" t="s">
         <v>670</v>
       </c>
       <c r="E502">
@@ -39423,7 +39430,7 @@
       <c r="C504">
         <v>4457811</v>
       </c>
-      <c r="D504" t="s">
+      <c r="D504" s="3" t="s">
         <v>422</v>
       </c>
       <c r="E504">
@@ -39491,7 +39498,7 @@
       <c r="C505">
         <v>2859643</v>
       </c>
-      <c r="D505" t="s">
+      <c r="D505" s="3" t="s">
         <v>564</v>
       </c>
       <c r="E505">
@@ -39562,7 +39569,7 @@
       <c r="C506">
         <v>4375167</v>
       </c>
-      <c r="D506" t="s">
+      <c r="D506" s="3" t="s">
         <v>525</v>
       </c>
       <c r="E506">
@@ -39630,7 +39637,7 @@
       <c r="C507">
         <v>0</v>
       </c>
-      <c r="D507" t="s">
+      <c r="D507" s="3" t="s">
         <v>644</v>
       </c>
       <c r="E507">
@@ -39701,7 +39708,7 @@
       <c r="C508">
         <v>0</v>
       </c>
-      <c r="D508" t="s">
+      <c r="D508" s="3" t="s">
         <v>640</v>
       </c>
       <c r="E508">
@@ -39772,7 +39779,7 @@
       <c r="C509">
         <v>2859643</v>
       </c>
-      <c r="D509" t="s">
+      <c r="D509" s="3" t="s">
         <v>564</v>
       </c>
       <c r="E509">
@@ -39843,7 +39850,7 @@
       <c r="C510">
         <v>2859643</v>
       </c>
-      <c r="D510" t="s">
+      <c r="D510" s="3" t="s">
         <v>564</v>
       </c>
       <c r="E510">
@@ -39914,7 +39921,7 @@
       <c r="C511">
         <v>4325844</v>
       </c>
-      <c r="D511" t="s">
+      <c r="D511" s="3" t="s">
         <v>639</v>
       </c>
       <c r="E511">
@@ -39982,7 +39989,7 @@
       <c r="C512">
         <v>2082567</v>
       </c>
-      <c r="D512" t="s">
+      <c r="D512" s="3" t="s">
         <v>111</v>
       </c>
       <c r="E512">
@@ -40053,7 +40060,7 @@
       <c r="C513">
         <v>4427456</v>
       </c>
-      <c r="D513" t="s">
+      <c r="D513" s="3" t="s">
         <v>399</v>
       </c>
       <c r="E513">
@@ -40121,7 +40128,7 @@
       <c r="C514">
         <v>2049182</v>
       </c>
-      <c r="D514" t="s">
+      <c r="D514" s="3" t="s">
         <v>608</v>
       </c>
       <c r="E514">
@@ -40192,7 +40199,7 @@
       <c r="C515">
         <v>4266590</v>
       </c>
-      <c r="D515" t="s">
+      <c r="D515" s="3" t="s">
         <v>615</v>
       </c>
       <c r="E515">
@@ -40260,7 +40267,7 @@
       <c r="C516">
         <v>2797661</v>
       </c>
-      <c r="D516" t="s">
+      <c r="D516" s="3" t="s">
         <v>603</v>
       </c>
       <c r="E516">
@@ -40328,7 +40335,7 @@
       <c r="C517">
         <v>2784895</v>
       </c>
-      <c r="D517" t="s">
+      <c r="D517" s="3" t="s">
         <v>591</v>
       </c>
       <c r="E517">
@@ -40396,7 +40403,7 @@
       <c r="C518">
         <v>2286964</v>
       </c>
-      <c r="D518" t="s">
+      <c r="D518" s="3" t="s">
         <v>611</v>
       </c>
       <c r="E518">
@@ -40464,7 +40471,7 @@
       <c r="C519">
         <v>2774601</v>
       </c>
-      <c r="D519" t="s">
+      <c r="D519" s="3" t="s">
         <v>591</v>
       </c>
       <c r="E519">
@@ -40535,7 +40542,7 @@
       <c r="C520">
         <v>2892738</v>
       </c>
-      <c r="D520" t="s">
+      <c r="D520" s="3" t="s">
         <v>589</v>
       </c>
       <c r="E520">
@@ -40606,7 +40613,7 @@
       <c r="C521">
         <v>9762846</v>
       </c>
-      <c r="D521" t="s">
+      <c r="D521" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E521">
@@ -40677,7 +40684,7 @@
       <c r="C522">
         <v>2867601</v>
       </c>
-      <c r="D522" t="s">
+      <c r="D522" s="3" t="s">
         <v>564</v>
       </c>
       <c r="E522">
@@ -40748,7 +40755,7 @@
       <c r="C523">
         <v>2570147</v>
       </c>
-      <c r="D523" t="s">
+      <c r="D523" s="3" t="s">
         <v>593</v>
       </c>
       <c r="E523">
@@ -40819,7 +40826,7 @@
       <c r="C524">
         <v>2323334</v>
       </c>
-      <c r="D524" t="s">
+      <c r="D524" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E524">
@@ -40890,7 +40897,7 @@
       <c r="C525">
         <v>2332326</v>
       </c>
-      <c r="D525" t="s">
+      <c r="D525" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E525">
@@ -40961,7 +40968,7 @@
       <c r="C526">
         <v>2570661</v>
       </c>
-      <c r="D526" t="s">
+      <c r="D526" s="3" t="s">
         <v>593</v>
       </c>
       <c r="E526">
@@ -41032,7 +41039,7 @@
       <c r="C527">
         <v>2041666</v>
       </c>
-      <c r="D527" t="s">
+      <c r="D527" s="3" t="s">
         <v>608</v>
       </c>
       <c r="E527">
@@ -41103,7 +41110,7 @@
       <c r="C528">
         <v>2930772</v>
       </c>
-      <c r="D528" t="s">
+      <c r="D528" s="3" t="s">
         <v>592</v>
       </c>
       <c r="E528">
@@ -41174,7 +41181,7 @@
       <c r="C529">
         <v>2882417</v>
       </c>
-      <c r="D529" t="s">
+      <c r="D529" s="3" t="s">
         <v>589</v>
       </c>
       <c r="E529">
@@ -41245,7 +41252,7 @@
       <c r="C530">
         <v>4266590</v>
       </c>
-      <c r="D530" t="s">
+      <c r="D530" s="3" t="s">
         <v>615</v>
       </c>
       <c r="E530">
@@ -41313,7 +41320,7 @@
       <c r="C531">
         <v>7593044</v>
       </c>
-      <c r="D531" t="s">
+      <c r="D531" s="3" t="s">
         <v>228</v>
       </c>
       <c r="E531">
@@ -41384,7 +41391,7 @@
       <c r="C532">
         <v>4375167</v>
       </c>
-      <c r="D532" t="s">
+      <c r="D532" s="3" t="s">
         <v>525</v>
       </c>
       <c r="E532">
@@ -41452,7 +41459,7 @@
       <c r="C533">
         <v>2967289</v>
       </c>
-      <c r="D533" t="s">
+      <c r="D533" s="3" t="s">
         <v>594</v>
       </c>
       <c r="E533">
@@ -41523,7 +41530,7 @@
       <c r="C534">
         <v>4278388</v>
       </c>
-      <c r="D534" t="s">
+      <c r="D534" s="3" t="s">
         <v>615</v>
       </c>
       <c r="E534">
@@ -41591,7 +41598,7 @@
       <c r="C535">
         <v>4265620</v>
       </c>
-      <c r="D535" t="s">
+      <c r="D535" s="3" t="s">
         <v>615</v>
       </c>
       <c r="E535">
@@ -41659,7 +41666,7 @@
       <c r="C536">
         <v>4247696</v>
       </c>
-      <c r="D536" t="s">
+      <c r="D536" s="3" t="s">
         <v>418</v>
       </c>
       <c r="E536">
@@ -41727,7 +41734,7 @@
       <c r="C537">
         <v>2223393</v>
       </c>
-      <c r="D537" t="s">
+      <c r="D537" s="3" t="s">
         <v>557</v>
       </c>
       <c r="E537">
@@ -41798,7 +41805,7 @@
       <c r="C538">
         <v>0</v>
       </c>
-      <c r="D538" t="s">
+      <c r="D538" s="3" t="s">
         <v>582</v>
       </c>
       <c r="E538">
@@ -41869,7 +41876,7 @@
       <c r="C539">
         <v>0</v>
       </c>
-      <c r="D539" t="s">
+      <c r="D539" s="3" t="s">
         <v>579</v>
       </c>
       <c r="E539">
@@ -41940,7 +41947,7 @@
       <c r="C540">
         <v>0</v>
       </c>
-      <c r="D540" t="s">
+      <c r="D540" s="3" t="s">
         <v>573</v>
       </c>
       <c r="E540">
@@ -42011,7 +42018,7 @@
       <c r="C541">
         <v>9542170</v>
       </c>
-      <c r="D541" t="s">
+      <c r="D541" s="3" t="s">
         <v>549</v>
       </c>
       <c r="E541">
@@ -42082,7 +42089,7 @@
       <c r="C542">
         <v>7574839</v>
       </c>
-      <c r="D542" t="s">
+      <c r="D542" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E542">
@@ -42153,7 +42160,7 @@
       <c r="C543">
         <v>8069609</v>
       </c>
-      <c r="D543" t="s">
+      <c r="D543" s="3" t="s">
         <v>539</v>
       </c>
       <c r="E543">
@@ -42224,7 +42231,7 @@
       <c r="C544">
         <v>7633896</v>
       </c>
-      <c r="D544" t="s">
+      <c r="D544" s="3" t="s">
         <v>358</v>
       </c>
       <c r="E544">
@@ -42295,7 +42302,7 @@
       <c r="C545">
         <v>7943747</v>
       </c>
-      <c r="D545" t="s">
+      <c r="D545" s="3" t="s">
         <v>529</v>
       </c>
       <c r="E545">
@@ -42366,7 +42373,7 @@
       <c r="C546">
         <v>7694882</v>
       </c>
-      <c r="D546" t="s">
+      <c r="D546" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E546">
@@ -42437,7 +42444,7 @@
       <c r="C547">
         <v>7694882</v>
       </c>
-      <c r="D547" t="s">
+      <c r="D547" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E547">
@@ -42508,7 +42515,7 @@
       <c r="C548">
         <v>7575179</v>
       </c>
-      <c r="D548" t="s">
+      <c r="D548" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E548">
@@ -42579,7 +42586,7 @@
       <c r="C549">
         <v>7575179</v>
       </c>
-      <c r="D549" t="s">
+      <c r="D549" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E549">
@@ -42650,7 +42657,7 @@
       <c r="C550">
         <v>0</v>
       </c>
-      <c r="D550" t="s">
+      <c r="D550" s="3" t="s">
         <v>493</v>
       </c>
       <c r="E550">
@@ -42721,7 +42728,7 @@
       <c r="C551">
         <v>4366009</v>
       </c>
-      <c r="D551" t="s">
+      <c r="D551" s="3" t="s">
         <v>525</v>
       </c>
       <c r="E551">
@@ -42789,7 +42796,7 @@
       <c r="C552">
         <v>0</v>
       </c>
-      <c r="D552" t="s">
+      <c r="D552" s="3" t="s">
         <v>494</v>
       </c>
       <c r="E552">
@@ -42860,7 +42867,7 @@
       <c r="C553">
         <v>8043603</v>
       </c>
-      <c r="D553" t="s">
+      <c r="D553" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E553">
@@ -42931,7 +42938,7 @@
       <c r="C554">
         <v>7755248</v>
       </c>
-      <c r="D554" t="s">
+      <c r="D554" s="3" t="s">
         <v>517</v>
       </c>
       <c r="E554">
@@ -43002,7 +43009,7 @@
       <c r="C555">
         <v>0</v>
       </c>
-      <c r="D555" t="s">
+      <c r="D555" s="3" t="s">
         <v>493</v>
       </c>
       <c r="E555">
@@ -43073,7 +43080,7 @@
       <c r="C556">
         <v>2393220</v>
       </c>
-      <c r="D556" t="s">
+      <c r="D556" s="3" t="s">
         <v>507</v>
       </c>
       <c r="E556">
@@ -43144,7 +43151,7 @@
       <c r="C557">
         <v>7560208</v>
       </c>
-      <c r="D557" t="s">
+      <c r="D557" s="3" t="s">
         <v>501</v>
       </c>
       <c r="E557">
@@ -43215,7 +43222,7 @@
       <c r="C558">
         <v>0</v>
       </c>
-      <c r="D558" t="s">
+      <c r="D558" s="3" t="s">
         <v>494</v>
       </c>
       <c r="E558">
@@ -43286,7 +43293,7 @@
       <c r="C559">
         <v>9297396</v>
       </c>
-      <c r="D559" t="s">
+      <c r="D559" s="3" t="s">
         <v>500</v>
       </c>
       <c r="E559">
@@ -43357,7 +43364,7 @@
       <c r="C560">
         <v>0</v>
       </c>
-      <c r="D560" t="s">
+      <c r="D560" s="3" t="s">
         <v>494</v>
       </c>
       <c r="E560">
@@ -43428,7 +43435,7 @@
       <c r="C561">
         <v>0</v>
       </c>
-      <c r="D561" t="s">
+      <c r="D561" s="3" t="s">
         <v>493</v>
       </c>
       <c r="E561">
@@ -43499,7 +43506,7 @@
       <c r="C562">
         <v>7962983</v>
       </c>
-      <c r="D562" t="s">
+      <c r="D562" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E562">
@@ -43567,7 +43574,7 @@
       <c r="C563">
         <v>1819</v>
       </c>
-      <c r="D563" t="s">
+      <c r="D563" s="3" t="s">
         <v>395</v>
       </c>
       <c r="E563">
@@ -43638,7 +43645,7 @@
       <c r="C564">
         <v>7687753</v>
       </c>
-      <c r="D564" t="s">
+      <c r="D564" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E564">
@@ -43706,7 +43713,7 @@
       <c r="C565">
         <v>2243195</v>
       </c>
-      <c r="D565" t="s">
+      <c r="D565" s="3" t="s">
         <v>481</v>
       </c>
       <c r="E565">
@@ -43777,7 +43784,7 @@
       <c r="C566">
         <v>2243195</v>
       </c>
-      <c r="D566" t="s">
+      <c r="D566" s="3" t="s">
         <v>481</v>
       </c>
       <c r="E566">
@@ -43848,7 +43855,7 @@
       <c r="C567">
         <v>0</v>
       </c>
-      <c r="D567" t="s">
+      <c r="D567" s="3" t="s">
         <v>455</v>
       </c>
       <c r="E567">
@@ -43919,7 +43926,7 @@
       <c r="C568">
         <v>2195433</v>
       </c>
-      <c r="D568" t="s">
+      <c r="D568" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E568">
@@ -43990,7 +43997,7 @@
       <c r="C569">
         <v>2195433</v>
       </c>
-      <c r="D569" t="s">
+      <c r="D569" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E569">
@@ -44061,7 +44068,7 @@
       <c r="C570">
         <v>0</v>
       </c>
-      <c r="D570" t="s">
+      <c r="D570" s="3" t="s">
         <v>468</v>
       </c>
       <c r="E570">
@@ -44132,7 +44139,7 @@
       <c r="C571">
         <v>2195433</v>
       </c>
-      <c r="D571" t="s">
+      <c r="D571" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E571">
@@ -44203,7 +44210,7 @@
       <c r="C572">
         <v>9364648</v>
       </c>
-      <c r="D572" t="s">
+      <c r="D572" s="3" t="s">
         <v>460</v>
       </c>
       <c r="E572">
@@ -44274,7 +44281,7 @@
       <c r="C573">
         <v>0</v>
       </c>
-      <c r="D573" t="s">
+      <c r="D573" s="3" t="s">
         <v>458</v>
       </c>
       <c r="E573">
@@ -44345,7 +44352,7 @@
       <c r="C574">
         <v>9175</v>
       </c>
-      <c r="D574" t="s">
+      <c r="D574" s="3" t="s">
         <v>463</v>
       </c>
       <c r="E574">
@@ -44416,7 +44423,7 @@
       <c r="C575">
         <v>0</v>
       </c>
-      <c r="D575" t="s">
+      <c r="D575" s="3" t="s">
         <v>455</v>
       </c>
       <c r="E575">
@@ -44487,7 +44494,7 @@
       <c r="C576">
         <v>0</v>
       </c>
-      <c r="D576" t="s">
+      <c r="D576" s="3" t="s">
         <v>466</v>
       </c>
       <c r="E576">
@@ -44558,7 +44565,7 @@
       <c r="C577">
         <v>0</v>
       </c>
-      <c r="D577" t="s">
+      <c r="D577" s="3" t="s">
         <v>468</v>
       </c>
       <c r="E577">
@@ -44629,7 +44636,7 @@
       <c r="C578">
         <v>0</v>
       </c>
-      <c r="D578" t="s">
+      <c r="D578" s="3" t="s">
         <v>458</v>
       </c>
       <c r="E578">
@@ -44771,7 +44778,7 @@
       <c r="C580">
         <v>0</v>
       </c>
-      <c r="D580" t="s">
+      <c r="D580" s="3" t="s">
         <v>468</v>
       </c>
       <c r="E580">
@@ -44842,7 +44849,7 @@
       <c r="C581">
         <v>0</v>
       </c>
-      <c r="D581" t="s">
+      <c r="D581" s="3" t="s">
         <v>473</v>
       </c>
       <c r="E581">
@@ -44913,7 +44920,7 @@
       <c r="C582">
         <v>4521535</v>
       </c>
-      <c r="D582" t="s">
+      <c r="D582" s="3" t="s">
         <v>403</v>
       </c>
       <c r="E582">
@@ -44981,7 +44988,7 @@
       <c r="C583">
         <v>9730948</v>
       </c>
-      <c r="D583" t="s">
+      <c r="D583" s="3" t="s">
         <v>451</v>
       </c>
       <c r="E583">
@@ -45052,7 +45059,7 @@
       <c r="C584">
         <v>4287850</v>
       </c>
-      <c r="D584" t="s">
+      <c r="D584" s="3" t="s">
         <v>444</v>
       </c>
       <c r="E584">
@@ -45120,7 +45127,7 @@
       <c r="C585">
         <v>4</v>
       </c>
-      <c r="D585" t="s">
+      <c r="D585" s="3" t="s">
         <v>437</v>
       </c>
       <c r="E585">
@@ -45191,7 +45198,7 @@
       <c r="C586">
         <v>17</v>
       </c>
-      <c r="D586" t="s">
+      <c r="D586" s="3" t="s">
         <v>432</v>
       </c>
       <c r="E586">
@@ -45262,7 +45269,7 @@
       <c r="C587">
         <v>4566319</v>
       </c>
-      <c r="D587" t="s">
+      <c r="D587" s="3" t="s">
         <v>427</v>
       </c>
       <c r="E587">
@@ -45330,7 +45337,7 @@
       <c r="C588">
         <v>4566316</v>
       </c>
-      <c r="D588" t="s">
+      <c r="D588" s="3" t="s">
         <v>427</v>
       </c>
       <c r="E588">
@@ -45398,7 +45405,7 @@
       <c r="C589">
         <v>4566309</v>
       </c>
-      <c r="D589" t="s">
+      <c r="D589" s="3" t="s">
         <v>427</v>
       </c>
       <c r="E589">
@@ -45466,7 +45473,7 @@
       <c r="C590">
         <v>4468642</v>
       </c>
-      <c r="D590" t="s">
+      <c r="D590" s="3" t="s">
         <v>422</v>
       </c>
       <c r="E590">
@@ -45670,7 +45677,7 @@
       <c r="C593">
         <v>9437190</v>
       </c>
-      <c r="D593" t="s">
+      <c r="D593" s="3" t="s">
         <v>420</v>
       </c>
       <c r="E593">
@@ -45812,7 +45819,7 @@
       <c r="C595">
         <v>4247971</v>
       </c>
-      <c r="D595" t="s">
+      <c r="D595" s="3" t="s">
         <v>418</v>
       </c>
       <c r="E595">
@@ -45880,7 +45887,7 @@
       <c r="C596">
         <v>4</v>
       </c>
-      <c r="D596" t="s">
+      <c r="D596" s="3" t="s">
         <v>409</v>
       </c>
       <c r="E596">
@@ -45951,7 +45958,7 @@
       <c r="C597">
         <v>0</v>
       </c>
-      <c r="D597" t="s">
+      <c r="D597" s="3" t="s">
         <v>405</v>
       </c>
       <c r="E597">
@@ -46022,7 +46029,7 @@
       <c r="C598">
         <v>4522833</v>
       </c>
-      <c r="D598" t="s">
+      <c r="D598" s="3" t="s">
         <v>403</v>
       </c>
       <c r="E598">
@@ -46090,7 +46097,7 @@
       <c r="C599">
         <v>9746609</v>
       </c>
-      <c r="D599" t="s">
+      <c r="D599" s="3" t="s">
         <v>351</v>
       </c>
       <c r="E599">
@@ -46161,7 +46168,7 @@
       <c r="C600">
         <v>2012517</v>
       </c>
-      <c r="D600" t="s">
+      <c r="D600" s="3" t="s">
         <v>373</v>
       </c>
       <c r="E600">
@@ -46232,7 +46239,7 @@
       <c r="C601">
         <v>8715</v>
       </c>
-      <c r="D601" t="s">
+      <c r="D601" s="3" t="s">
         <v>276</v>
       </c>
       <c r="E601">
@@ -46303,7 +46310,7 @@
       <c r="C602">
         <v>9781347</v>
       </c>
-      <c r="D602" t="s">
+      <c r="D602" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E602">
@@ -46374,7 +46381,7 @@
       <c r="C603">
         <v>9378033</v>
       </c>
-      <c r="D603" t="s">
+      <c r="D603" s="3" t="s">
         <v>279</v>
       </c>
       <c r="E603">
@@ -46445,7 +46452,7 @@
       <c r="C604">
         <v>7875582</v>
       </c>
-      <c r="D604" t="s">
+      <c r="D604" s="3" t="s">
         <v>324</v>
       </c>
       <c r="E604">
@@ -46516,7 +46523,7 @@
       <c r="C605">
         <v>4411914</v>
       </c>
-      <c r="D605" t="s">
+      <c r="D605" s="3" t="s">
         <v>399</v>
       </c>
       <c r="E605">
@@ -46584,7 +46591,7 @@
       <c r="C606">
         <v>0</v>
       </c>
-      <c r="D606" t="s">
+      <c r="D606" s="3" t="s">
         <v>253</v>
       </c>
       <c r="E606">
@@ -46655,7 +46662,7 @@
       <c r="C607">
         <v>941</v>
       </c>
-      <c r="D607" t="s">
+      <c r="D607" s="3" t="s">
         <v>253</v>
       </c>
       <c r="E607">
@@ -46726,7 +46733,7 @@
       <c r="C608">
         <v>5</v>
       </c>
-      <c r="D608" t="s">
+      <c r="D608" s="3" t="s">
         <v>369</v>
       </c>
       <c r="E608">
@@ -46797,7 +46804,7 @@
       <c r="C609">
         <v>0</v>
       </c>
-      <c r="D609" t="s">
+      <c r="D609" s="3" t="s">
         <v>332</v>
       </c>
       <c r="E609">
@@ -46868,7 +46875,7 @@
       <c r="C610">
         <v>8</v>
       </c>
-      <c r="D610" t="s">
+      <c r="D610" s="3" t="s">
         <v>369</v>
       </c>
       <c r="E610">
@@ -46939,7 +46946,7 @@
       <c r="C611">
         <v>0</v>
       </c>
-      <c r="D611" t="s">
+      <c r="D611" s="3" t="s">
         <v>369</v>
       </c>
       <c r="E611">
@@ -47010,7 +47017,7 @@
       <c r="C612">
         <v>0</v>
       </c>
-      <c r="D612" t="s">
+      <c r="D612" s="3" t="s">
         <v>283</v>
       </c>
       <c r="E612">
@@ -47081,7 +47088,7 @@
       <c r="C613">
         <v>9</v>
       </c>
-      <c r="D613" t="s">
+      <c r="D613" s="3" t="s">
         <v>283</v>
       </c>
       <c r="E613">
@@ -47152,7 +47159,7 @@
       <c r="C614">
         <v>0</v>
       </c>
-      <c r="D614" t="s">
+      <c r="D614" s="3" t="s">
         <v>276</v>
       </c>
       <c r="E614">
@@ -47223,7 +47230,7 @@
       <c r="C615">
         <v>383</v>
       </c>
-      <c r="D615" t="s">
+      <c r="D615" s="3" t="s">
         <v>338</v>
       </c>
       <c r="E615">
@@ -47294,7 +47301,7 @@
       <c r="C616">
         <v>383</v>
       </c>
-      <c r="D616" t="s">
+      <c r="D616" s="3" t="s">
         <v>338</v>
       </c>
       <c r="E616">
@@ -47365,7 +47372,7 @@
       <c r="C617">
         <v>0</v>
       </c>
-      <c r="D617" t="s">
+      <c r="D617" s="3" t="s">
         <v>332</v>
       </c>
       <c r="E617">
@@ -47436,7 +47443,7 @@
       <c r="C618">
         <v>0</v>
       </c>
-      <c r="D618" t="s">
+      <c r="D618" s="3" t="s">
         <v>332</v>
       </c>
       <c r="E618">
@@ -47507,7 +47514,7 @@
       <c r="C619">
         <v>4400000</v>
       </c>
-      <c r="D619" t="s">
+      <c r="D619" s="3" t="s">
         <v>369</v>
       </c>
       <c r="E619">
@@ -47578,7 +47585,7 @@
       <c r="C620">
         <v>0</v>
       </c>
-      <c r="D620" t="s">
+      <c r="D620" s="3" t="s">
         <v>303</v>
       </c>
       <c r="E620">
@@ -47649,7 +47656,7 @@
       <c r="C621">
         <v>8</v>
       </c>
-      <c r="D621" t="s">
+      <c r="D621" s="3" t="s">
         <v>332</v>
       </c>
       <c r="E621">
@@ -47720,7 +47727,7 @@
       <c r="C622">
         <v>9927975</v>
       </c>
-      <c r="D622" t="s">
+      <c r="D622" s="3" t="s">
         <v>320</v>
       </c>
       <c r="E622">
@@ -47791,7 +47798,7 @@
       <c r="C623">
         <v>9655476</v>
       </c>
-      <c r="D623" t="s">
+      <c r="D623" s="3" t="s">
         <v>346</v>
       </c>
       <c r="E623">
@@ -47862,7 +47869,7 @@
       <c r="C624">
         <v>7574504</v>
       </c>
-      <c r="D624" t="s">
+      <c r="D624" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E624">
@@ -47933,7 +47940,7 @@
       <c r="C625">
         <v>149</v>
       </c>
-      <c r="D625" t="s">
+      <c r="D625" s="3" t="s">
         <v>276</v>
       </c>
       <c r="E625">
@@ -48001,7 +48008,7 @@
       <c r="C626">
         <v>2754</v>
       </c>
-      <c r="D626" t="s">
+      <c r="D626" s="3" t="s">
         <v>276</v>
       </c>
       <c r="E626">
@@ -48072,7 +48079,7 @@
       <c r="C627">
         <v>7628406</v>
       </c>
-      <c r="D627" t="s">
+      <c r="D627" s="3" t="s">
         <v>358</v>
       </c>
       <c r="E627">
@@ -48143,7 +48150,7 @@
       <c r="C628">
         <v>8046180</v>
       </c>
-      <c r="D628" t="s">
+      <c r="D628" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E628">
@@ -48214,7 +48221,7 @@
       <c r="C629">
         <v>700</v>
       </c>
-      <c r="D629" t="s">
+      <c r="D629" s="3" t="s">
         <v>256</v>
       </c>
       <c r="E629">
@@ -48285,7 +48292,7 @@
       <c r="C630">
         <v>9712431</v>
       </c>
-      <c r="D630" t="s">
+      <c r="D630" s="3" t="s">
         <v>277</v>
       </c>
       <c r="E630">
@@ -48356,7 +48363,7 @@
       <c r="C631">
         <v>2195433</v>
       </c>
-      <c r="D631" t="s">
+      <c r="D631" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E631">
@@ -48427,7 +48434,7 @@
       <c r="C632">
         <v>33</v>
       </c>
-      <c r="D632" t="s">
+      <c r="D632" s="3" t="s">
         <v>289</v>
       </c>
       <c r="E632">
@@ -48498,7 +48505,7 @@
       <c r="C633">
         <v>3841151</v>
       </c>
-      <c r="D633" t="s">
+      <c r="D633" s="3" t="s">
         <v>385</v>
       </c>
       <c r="E633">
@@ -48563,7 +48570,7 @@
       <c r="C634">
         <v>3841151</v>
       </c>
-      <c r="D634" t="s">
+      <c r="D634" s="3" t="s">
         <v>385</v>
       </c>
       <c r="E634">
@@ -48628,7 +48635,7 @@
       <c r="C635">
         <v>0</v>
       </c>
-      <c r="D635" t="s">
+      <c r="D635" s="3" t="s">
         <v>253</v>
       </c>
       <c r="E635">
@@ -48699,7 +48706,7 @@
       <c r="C636">
         <v>74139</v>
       </c>
-      <c r="D636" t="s">
+      <c r="D636" s="3" t="s">
         <v>243</v>
       </c>
       <c r="E636">
@@ -48770,7 +48777,7 @@
       <c r="C637">
         <v>70</v>
       </c>
-      <c r="D637" t="s">
+      <c r="D637" s="3" t="s">
         <v>256</v>
       </c>
       <c r="E637">
@@ -48835,7 +48842,7 @@
       <c r="C638">
         <v>611</v>
       </c>
-      <c r="D638" t="s">
+      <c r="D638" s="3" t="s">
         <v>146</v>
       </c>
       <c r="E638">
@@ -48906,7 +48913,7 @@
       <c r="C639">
         <v>3</v>
       </c>
-      <c r="D639" t="s">
+      <c r="D639" s="3" t="s">
         <v>283</v>
       </c>
       <c r="E639">
@@ -48974,7 +48981,7 @@
       <c r="C640">
         <v>0</v>
       </c>
-      <c r="D640" t="s">
+      <c r="D640" s="3" t="s">
         <v>395</v>
       </c>
       <c r="E640">
@@ -49045,7 +49052,7 @@
       <c r="C641">
         <v>0</v>
       </c>
-      <c r="D641" t="s">
+      <c r="D641" s="3" t="s">
         <v>276</v>
       </c>
       <c r="E641">
@@ -49116,7 +49123,7 @@
       <c r="C642">
         <v>0</v>
       </c>
-      <c r="D642" t="s">
+      <c r="D642" s="3" t="s">
         <v>253</v>
       </c>
       <c r="E642">
@@ -49187,7 +49194,7 @@
       <c r="C643">
         <v>0</v>
       </c>
-      <c r="D643" t="s">
+      <c r="D643" s="3" t="s">
         <v>243</v>
       </c>
       <c r="E643">
@@ -49258,7 +49265,7 @@
       <c r="C644">
         <v>780</v>
       </c>
-      <c r="D644" t="s">
+      <c r="D644" s="3" t="s">
         <v>259</v>
       </c>
       <c r="E644">
@@ -49326,7 +49333,7 @@
       <c r="C645">
         <v>6</v>
       </c>
-      <c r="D645" t="s">
+      <c r="D645" s="3" t="s">
         <v>259</v>
       </c>
       <c r="E645">
@@ -49397,7 +49404,7 @@
       <c r="C646">
         <v>700</v>
       </c>
-      <c r="D646" t="s">
+      <c r="D646" s="3" t="s">
         <v>256</v>
       </c>
       <c r="E646">
@@ -49468,7 +49475,7 @@
       <c r="C647">
         <v>0</v>
       </c>
-      <c r="D647" t="s">
+      <c r="D647" s="3" t="s">
         <v>253</v>
       </c>
       <c r="E647">
@@ -49539,7 +49546,7 @@
       <c r="C648">
         <v>7650220</v>
       </c>
-      <c r="D648" t="s">
+      <c r="D648" s="3" t="s">
         <v>248</v>
       </c>
       <c r="E648">
@@ -49610,7 +49617,7 @@
       <c r="C649">
         <v>74139</v>
       </c>
-      <c r="D649" t="s">
+      <c r="D649" s="3" t="s">
         <v>243</v>
       </c>
       <c r="E649">
@@ -49681,7 +49688,7 @@
       <c r="C650">
         <v>9411631</v>
       </c>
-      <c r="D650" t="s">
+      <c r="D650" s="3" t="s">
         <v>238</v>
       </c>
       <c r="E650">
@@ -49752,7 +49759,7 @@
       <c r="C651">
         <v>0</v>
       </c>
-      <c r="D651" t="s">
+      <c r="D651" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E651">
@@ -49823,7 +49830,7 @@
       <c r="C652">
         <v>9781347</v>
       </c>
-      <c r="D652" t="s">
+      <c r="D652" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E652">
@@ -49894,7 +49901,7 @@
       <c r="C653">
         <v>9579607</v>
       </c>
-      <c r="D653" t="s">
+      <c r="D653" s="3" t="s">
         <v>204</v>
       </c>
       <c r="E653">
@@ -49965,7 +49972,7 @@
       <c r="C654">
         <v>0</v>
       </c>
-      <c r="D654" t="s">
+      <c r="D654" s="3" t="s">
         <v>190</v>
       </c>
       <c r="E654">
@@ -50107,7 +50114,7 @@
       <c r="C656">
         <v>0</v>
       </c>
-      <c r="D656" t="s">
+      <c r="D656" s="3" t="s">
         <v>183</v>
       </c>
       <c r="E656">
@@ -50178,7 +50185,7 @@
       <c r="C657">
         <v>9612557</v>
       </c>
-      <c r="D657" t="s">
+      <c r="D657" s="3" t="s">
         <v>176</v>
       </c>
       <c r="E657">
@@ -50249,7 +50256,7 @@
       <c r="C658">
         <v>0</v>
       </c>
-      <c r="D658" t="s">
+      <c r="D658" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E658">
@@ -50320,7 +50327,7 @@
       <c r="C659">
         <v>0</v>
       </c>
-      <c r="D659" t="s">
+      <c r="D659" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E659">
@@ -50391,7 +50398,7 @@
       <c r="C660">
         <v>7732931</v>
       </c>
-      <c r="D660" t="s">
+      <c r="D660" s="3" t="s">
         <v>144</v>
       </c>
       <c r="E660">
@@ -50462,7 +50469,7 @@
       <c r="C661">
         <v>7571178</v>
       </c>
-      <c r="D661" t="s">
+      <c r="D661" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E661">
@@ -50533,7 +50540,7 @@
       <c r="C662">
         <v>7725594</v>
       </c>
-      <c r="D662" t="s">
+      <c r="D662" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E662">
@@ -50604,7 +50611,7 @@
       <c r="C663">
         <v>8108448</v>
       </c>
-      <c r="D663" t="s">
+      <c r="D663" s="3" t="s">
         <v>156</v>
       </c>
       <c r="E663">
@@ -50746,7 +50753,7 @@
       <c r="C665">
         <v>2185872</v>
       </c>
-      <c r="D665" t="s">
+      <c r="D665" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E665">
@@ -50817,7 +50824,7 @@
       <c r="C666">
         <v>7973255</v>
       </c>
-      <c r="D666" t="s">
+      <c r="D666" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E666">
@@ -50888,7 +50895,7 @@
       <c r="C667">
         <v>8057614</v>
       </c>
-      <c r="D667" t="s">
+      <c r="D667" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E667">
@@ -50959,7 +50966,7 @@
       <c r="C668">
         <v>7722717</v>
       </c>
-      <c r="D668" t="s">
+      <c r="D668" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E668">
@@ -51030,7 +51037,7 @@
       <c r="C669">
         <v>7722717</v>
       </c>
-      <c r="D669" t="s">
+      <c r="D669" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E669">
@@ -51101,7 +51108,7 @@
       <c r="C670">
         <v>2095230</v>
       </c>
-      <c r="D670" t="s">
+      <c r="D670" s="3" t="s">
         <v>111</v>
       </c>
       <c r="E670">
@@ -51172,7 +51179,7 @@
       <c r="C671">
         <v>2199059</v>
       </c>
-      <c r="D671" t="s">
+      <c r="D671" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E671">
@@ -51243,7 +51250,7 @@
       <c r="C672">
         <v>9881925</v>
       </c>
-      <c r="D672" t="s">
+      <c r="D672" s="3" t="s">
         <v>94</v>
       </c>
       <c r="E672">
@@ -51314,7 +51321,7 @@
       <c r="C673">
         <v>9903723</v>
       </c>
-      <c r="D673" t="s">
+      <c r="D673" s="3" t="s">
         <v>101</v>
       </c>
       <c r="E673">
@@ -51385,7 +51392,7 @@
       <c r="C674">
         <v>7883997</v>
       </c>
-      <c r="D674" t="s">
+      <c r="D674" s="3" t="s">
         <v>92</v>
       </c>
       <c r="E674">
@@ -51456,7 +51463,7 @@
       <c r="C675">
         <v>7883997</v>
       </c>
-      <c r="D675" t="s">
+      <c r="D675" s="3" t="s">
         <v>92</v>
       </c>
       <c r="E675">
@@ -51527,7 +51534,7 @@
       <c r="C676">
         <v>7612655</v>
       </c>
-      <c r="D676" t="s">
+      <c r="D676" s="3" t="s">
         <v>84</v>
       </c>
       <c r="E676">
@@ -51598,7 +51605,7 @@
       <c r="C677">
         <v>2327231</v>
       </c>
-      <c r="D677" t="s">
+      <c r="D677" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E677">
@@ -51669,7 +51676,7 @@
       <c r="C678">
         <v>7698912</v>
       </c>
-      <c r="D678" t="s">
+      <c r="D678" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E678">
@@ -51740,7 +51747,7 @@
       <c r="C679">
         <v>7698912</v>
       </c>
-      <c r="D679" t="s">
+      <c r="D679" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E679">
@@ -51811,7 +51818,7 @@
       <c r="C680">
         <v>7847150</v>
       </c>
-      <c r="D680" t="s">
+      <c r="D680" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E680">
@@ -51882,7 +51889,7 @@
       <c r="C681">
         <v>7846324</v>
       </c>
-      <c r="D681" t="s">
+      <c r="D681" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E681">
@@ -51953,7 +51960,7 @@
       <c r="C682">
         <v>2361847</v>
       </c>
-      <c r="D682" t="s">
+      <c r="D682" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E682">
@@ -52024,7 +52031,7 @@
       <c r="C683">
         <v>8036705</v>
       </c>
-      <c r="D683" t="s">
+      <c r="D683" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E683">
